--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14916,7 +14916,7 @@
       <c r="G501" t="inlineStr"/>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
-        <v>4.642658630399083</v>
+        <v>4.642080540008188</v>
       </c>
       <c r="J501" t="n">
         <v>4.363913651397029</v>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K501"/>
+  <dimension ref="A1:K502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9114,7 +9114,7 @@
         <v>1.4250909</v>
       </c>
       <c r="D318" t="n">
-        <v>4.653960350157523</v>
+        <v>4.654912277882906</v>
       </c>
       <c r="E318" t="n">
         <v>4.672828834461906</v>
@@ -9178,7 +9178,7 @@
         <v>1.597619</v>
       </c>
       <c r="D320" t="n">
-        <v>4.634728988229636</v>
+        <v>4.635699391022914</v>
       </c>
       <c r="E320" t="n">
         <v>4.654912277882906</v>
@@ -10318,7 +10318,7 @@
         <v>0.2050435</v>
       </c>
       <c r="D356" t="n">
-        <v>4.506454213048934</v>
+        <v>4.507557357121091</v>
       </c>
       <c r="E356" t="n">
         <v>4.629862798578463</v>
@@ -10667,7 +10667,7 @@
         <v>-0.0139091</v>
       </c>
       <c r="D367" t="n">
-        <v>4.56746831880408</v>
+        <v>4.5685062016165</v>
       </c>
       <c r="E367" t="n">
         <v>4.632785353021065</v>
@@ -11047,7 +11047,7 @@
         <v>-0.2679091</v>
       </c>
       <c r="D379" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="E379" t="n">
         <v>4.623010104116422</v>
@@ -11869,7 +11869,7 @@
         <v>-0.319</v>
       </c>
       <c r="D405" t="n">
-        <v>4.650143551630823</v>
+        <v>4.651099117876491</v>
       </c>
       <c r="E405" t="n">
         <v>4.669083511731744</v>
@@ -11902,7 +11902,7 @@
         <v>-0.31885</v>
       </c>
       <c r="D406" t="n">
-        <v>4.638604962074329</v>
+        <v>4.637637376125593</v>
       </c>
       <c r="E406" t="n">
         <v>4.65681341913993</v>
@@ -12567,7 +12567,7 @@
         <v>-0.376</v>
       </c>
       <c r="D427" t="n">
-        <v>4.348986780595681</v>
+        <v>4.350277936359301</v>
       </c>
       <c r="E427" t="n">
         <v>4.532599493153256</v>
@@ -12598,7 +12598,7 @@
         <v>-0.4441304</v>
       </c>
       <c r="D428" t="n">
-        <v>4.422448549172797</v>
+        <v>4.423648309364701</v>
       </c>
       <c r="E428" t="n">
         <v>4.576770711466393</v>
@@ -12629,7 +12629,7 @@
         <v>-0.4797143</v>
       </c>
       <c r="D429" t="n">
-        <v>4.542230386214217</v>
+        <v>4.543294782270004</v>
       </c>
       <c r="E429" t="n">
         <v>4.585987366571318</v>
@@ -12914,7 +12914,7 @@
         <v>-0.5400952</v>
       </c>
       <c r="D438" t="n">
-        <v>4.691347882229143</v>
+        <v>4.692264892839025</v>
       </c>
       <c r="E438" t="n">
         <v>4.606169686321175</v>
@@ -13042,7 +13042,7 @@
         <v>-0.5450455</v>
       </c>
       <c r="D442" t="n">
-        <v>4.731802836921458</v>
+        <v>4.730921391293652</v>
       </c>
       <c r="E442" t="n">
         <v>4.590056548178043</v>
@@ -13073,7 +13073,7 @@
         <v>-0.5498095</v>
       </c>
       <c r="D443" t="n">
-        <v>4.740574822994295</v>
+        <v>4.739701078945697</v>
       </c>
       <c r="E443" t="n">
         <v>4.618086411254637</v>
@@ -13104,7 +13104,7 @@
         <v>-0.5673636</v>
       </c>
       <c r="D444" t="n">
-        <v>4.760463070394127</v>
+        <v>4.75960653929251</v>
       </c>
       <c r="E444" t="n">
         <v>4.597138014290827</v>
@@ -13484,7 +13484,7 @@
         <v>1.8252273</v>
       </c>
       <c r="D456" t="n">
-        <v>4.553876891600541</v>
+        <v>4.552823705615882</v>
       </c>
       <c r="E456" t="n">
         <v>4.616110126026426</v>
@@ -13517,7 +13517,7 @@
         <v>2.0634762</v>
       </c>
       <c r="D457" t="n">
-        <v>4.551769409260976</v>
+        <v>4.550714000192032</v>
       </c>
       <c r="E457" t="n">
         <v>4.623991940228679</v>
@@ -13548,7 +13548,7 @@
         <v>2.3448636</v>
       </c>
       <c r="D458" t="n">
-        <v>4.591071261608589</v>
+        <v>4.590056548178043</v>
       </c>
       <c r="E458" t="n">
         <v>4.609162207257629</v>
@@ -13707,7 +13707,7 @@
         <v>3.5358636</v>
       </c>
       <c r="D463" t="n">
-        <v>4.583946549536464</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="E463" t="n">
         <v>4.622027303054514</v>
@@ -13738,7 +13738,7 @@
         <v>3.6718095</v>
       </c>
       <c r="D464" t="n">
-        <v>4.558078578454241</v>
+        <v>4.559126247486684</v>
       </c>
       <c r="E464" t="n">
         <v>4.620058798481842</v>
@@ -13769,7 +13769,7 @@
         <v>3.7803043</v>
       </c>
       <c r="D465" t="n">
-        <v>4.540098189244376</v>
+        <v>4.541164856012179</v>
       </c>
       <c r="E465" t="n">
         <v>4.619073091157083</v>
@@ -13802,7 +13802,7 @@
         <v>3.8800476</v>
       </c>
       <c r="D466" t="n">
-        <v>4.571613402459248</v>
+        <v>4.570578741218473</v>
       </c>
       <c r="E466" t="n">
         <v>4.619073091157083</v>
@@ -13833,7 +13833,7 @@
         <v>3.9676364</v>
       </c>
       <c r="D467" t="n">
-        <v>4.545420181582317</v>
+        <v>4.544358046591334</v>
       </c>
       <c r="E467" t="n">
         <v>4.620058798481842</v>
@@ -14118,7 +14118,7 @@
         <v>3.6848261</v>
       </c>
       <c r="D476" t="n">
-        <v>4.558078578454241</v>
+        <v>4.559126247486684</v>
       </c>
       <c r="E476" t="n">
         <v>4.623010104116422</v>
@@ -14244,7 +14244,7 @@
         <v>3.0067619</v>
       </c>
       <c r="D480" t="n">
-        <v>4.56954300834494</v>
+        <v>4.5685062016165</v>
       </c>
       <c r="E480" t="n">
         <v>4.621043535144381</v>
@@ -14277,7 +14277,7 @@
         <v>2.8246</v>
       </c>
       <c r="D481" t="n">
-        <v>4.531523645819793</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="E481" t="n">
         <v>4.617098756853365</v>
@@ -14434,7 +14434,7 @@
         <v>2.0872381</v>
       </c>
       <c r="D486" t="n">
-        <v>4.537961436294641</v>
+        <v>4.539030383483547</v>
       </c>
       <c r="E486" t="n">
         <v>4.60816569496789</v>
@@ -14467,7 +14467,7 @@
         <v>1.983619</v>
       </c>
       <c r="D487" t="n">
-        <v>4.503137460422939</v>
+        <v>4.504244267398131</v>
       </c>
       <c r="E487" t="n">
         <v>4.640537329825382</v>
@@ -14498,7 +14498,7 @@
         <v>1.9863478</v>
       </c>
       <c r="D488" t="n">
-        <v>4.528289141652134</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="E488" t="n">
         <v>4.641502115235482</v>
@@ -14529,7 +14529,7 @@
         <v>2.0210952</v>
       </c>
       <c r="D489" t="n">
-        <v>4.528289141652134</v>
+        <v>4.529368472571809</v>
       </c>
       <c r="E489" t="n">
         <v>4.626931677769604</v>
@@ -14562,7 +14562,7 @@
         <v>2.0272727</v>
       </c>
       <c r="D490" t="n">
-        <v>4.533674184283021</v>
+        <v>4.532599493153256</v>
       </c>
       <c r="E490" t="n">
         <v>4.636668853047462</v>
@@ -14593,7 +14593,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.552823705615882</v>
+        <v>4.551769409260976</v>
       </c>
       <c r="E491" t="n">
         <v>4.637637376125593</v>
@@ -14624,7 +14624,7 @@
         <v>2.04165</v>
       </c>
       <c r="D492" t="n">
-        <v>4.558078578454241</v>
+        <v>4.557029810660157</v>
       </c>
       <c r="E492" t="n">
         <v>4.638604962074329</v>
@@ -14657,7 +14657,7 @@
         <v>2.0484286</v>
       </c>
       <c r="D493" t="n">
-        <v>4.548599834499697</v>
+        <v>4.547541073151455</v>
       </c>
       <c r="E493" t="n">
         <v>4.632785353021065</v>
@@ -14752,7 +14752,7 @@
         <v>2.1094091</v>
       </c>
       <c r="D496" t="n">
-        <v>4.560172820057356</v>
+        <v>4.561218298458908</v>
       </c>
       <c r="E496" t="n">
         <v>4.640537329825382</v>
@@ -14783,7 +14783,7 @@
         <v>2.1753</v>
       </c>
       <c r="D497" t="n">
-        <v>4.530446639792155</v>
+        <v>4.531523645819793</v>
       </c>
       <c r="E497" t="n">
         <v>4.640537329825382</v>
@@ -14814,7 +14814,7 @@
         <v>2.2261</v>
       </c>
       <c r="D498" t="n">
-        <v>4.545420181582317</v>
+        <v>4.546481189639412</v>
       </c>
       <c r="E498" t="n">
         <v>4.640537329825382</v>
@@ -14847,7 +14847,7 @@
         <v>2.339</v>
       </c>
       <c r="D499" t="n">
-        <v>4.539030383483547</v>
+        <v>4.540098189244376</v>
       </c>
       <c r="E499" t="n">
         <v>4.639571612705423</v>
@@ -14878,7 +14878,7 @@
         <v>2.4253913</v>
       </c>
       <c r="D500" t="n">
-        <v>4.562262684976814</v>
+        <v>4.563305981889393</v>
       </c>
       <c r="E500" t="n">
         <v>4.635699391022914</v>
@@ -14909,7 +14909,7 @@
         <v>2.5131429</v>
       </c>
       <c r="D501" t="n">
-        <v>4.585987366571318</v>
+        <v>4.583946549536464</v>
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
@@ -14923,6 +14923,23 @@
       </c>
       <c r="K501" t="inlineStr"/>
     </row>
+    <row r="502">
+      <c r="A502" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="n">
+        <v>4.566429357671661</v>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -8743,7 +8743,7 @@
         <v>4.722953221644475</v>
       </c>
       <c r="G306" t="n">
-        <v>4.30406509320417</v>
+        <v>4.302712827954156</v>
       </c>
       <c r="H306" t="n">
         <v>9.300000000000001</v>
@@ -8966,7 +8966,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="G313" t="n">
-        <v>4.325456283185487</v>
+        <v>4.324132656254979</v>
       </c>
       <c r="H313" t="n">
         <v>9.199999999999999</v>
@@ -11467,7 +11467,7 @@
         <v>4.742320024135325</v>
       </c>
       <c r="G392" t="n">
-        <v>4.49647076906475</v>
+        <v>4.495355319980884</v>
       </c>
       <c r="H392" t="n">
         <v>9.6</v>
@@ -12227,7 +12227,7 @@
         <v>4.715816706075155</v>
       </c>
       <c r="G416" t="n">
-        <v>4.535820107853298</v>
+        <v>4.534747721691546</v>
       </c>
       <c r="H416" t="n">
         <v>8.4</v>
@@ -12576,7 +12576,7 @@
         <v>4.585987366571318</v>
       </c>
       <c r="G427" t="n">
-        <v>4.565389315976247</v>
+        <v>4.564348191467836</v>
       </c>
       <c r="H427" t="n">
         <v>7.4</v>
@@ -12607,7 +12607,7 @@
         <v>4.632785353021065</v>
       </c>
       <c r="G428" t="n">
-        <v>4.545420181582317</v>
+        <v>4.544358046591334</v>
       </c>
       <c r="H428" t="n">
         <v>8.6</v>
@@ -12987,7 +12987,7 @@
         <v>4.596129441335942</v>
       </c>
       <c r="G440" t="n">
-        <v>4.619073091157083</v>
+        <v>4.618086411254637</v>
       </c>
       <c r="H440" t="n">
         <v>8</v>
@@ -13113,7 +13113,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="G444" t="n">
-        <v>4.633757642840004</v>
+        <v>4.634728988229636</v>
       </c>
       <c r="H444" t="n">
         <v>7.4</v>
@@ -13303,7 +13303,7 @@
         <v>4.557029810660157</v>
       </c>
       <c r="G450" t="n">
-        <v>4.645351975620923</v>
+        <v>4.644390899141372</v>
       </c>
       <c r="H450" t="n">
         <v>7.5</v>
@@ -13621,7 +13621,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="G460" t="n">
-        <v>4.619073091157083</v>
+        <v>4.618086411254637</v>
       </c>
       <c r="H460" t="n">
         <v>7.1</v>
@@ -14127,7 +14127,7 @@
         <v>4.537961436294641</v>
       </c>
       <c r="G476" t="n">
-        <v>4.631812116934513</v>
+        <v>4.632785353021065</v>
       </c>
       <c r="H476" t="n">
         <v>7.5</v>
@@ -14191,7 +14191,7 @@
         <v>4.539030383483547</v>
       </c>
       <c r="G478" t="n">
-        <v>4.649187071404866</v>
+        <v>4.650143551630823</v>
       </c>
       <c r="H478" t="n">
         <v>7.5</v>
@@ -14253,7 +14253,7 @@
         <v>4.548599834499697</v>
       </c>
       <c r="G480" t="n">
-        <v>4.646312129319266</v>
+        <v>4.647271362006727</v>
       </c>
       <c r="H480" t="n">
         <v>7.4</v>
@@ -14286,7 +14286,7 @@
         <v>4.55597994179732</v>
       </c>
       <c r="G481" t="n">
-        <v>4.644390899141372</v>
+        <v>4.643428898105181</v>
       </c>
       <c r="H481" t="n">
         <v>7.3</v>
@@ -14381,7 +14381,7 @@
         <v>4.525044141508807</v>
       </c>
       <c r="G484" t="n">
-        <v>4.657762636107262</v>
+        <v>4.65681341913993</v>
       </c>
       <c r="H484" t="n">
         <v>7.6</v>
@@ -14507,7 +14507,7 @@
         <v>4.526126978647638</v>
       </c>
       <c r="G488" t="n">
-        <v>4.664382045619937</v>
+        <v>4.665324108807838</v>
       </c>
       <c r="H488" t="n">
         <v>7.7</v>
@@ -14538,7 +14538,7 @@
         <v>4.535820107853298</v>
       </c>
       <c r="G489" t="n">
-        <v>4.672828834461906</v>
+        <v>4.671893818030999</v>
       </c>
       <c r="H489" t="n">
         <v>7.8</v>
@@ -14602,7 +14602,7 @@
         <v>4.51085950651685</v>
       </c>
       <c r="G491" t="n">
-        <v>4.677490847567717</v>
+        <v>4.678420647727684</v>
       </c>
       <c r="H491" t="n">
         <v>8</v>
@@ -14633,7 +14633,7 @@
         <v>4.502029427068578</v>
       </c>
       <c r="G492" t="n">
-        <v>4.679349584162343</v>
+        <v>4.680277658474897</v>
       </c>
       <c r="H492" t="n">
         <v>8</v>
@@ -14666,7 +14666,7 @@
         <v>4.517431271680085</v>
       </c>
       <c r="G493" t="n">
-        <v>4.680277658474897</v>
+        <v>4.681204872264089</v>
       </c>
       <c r="H493" t="n">
         <v>8</v>
@@ -14697,7 +14697,7 @@
         <v>4.507557357121091</v>
       </c>
       <c r="G494" t="n">
-        <v>4.683981366412381</v>
+        <v>4.684905154006945</v>
       </c>
       <c r="H494" t="n">
         <v>8.1</v>
@@ -14728,7 +14728,7 @@
         <v>4.49423862528081</v>
       </c>
       <c r="G495" t="n">
-        <v>4.673762977453703</v>
+        <v>4.674696248636701</v>
       </c>
       <c r="H495" t="n">
         <v>8.199999999999999</v>
@@ -14761,7 +14761,7 @@
         <v>4.490881039585964</v>
       </c>
       <c r="G496" t="n">
-        <v>4.681204872264089</v>
+        <v>4.68213122712422</v>
       </c>
       <c r="H496" t="n">
         <v>8.199999999999999</v>
@@ -14792,7 +14792,7 @@
         <v>4.489759334476764</v>
       </c>
       <c r="G497" t="n">
-        <v>4.686750172980514</v>
+        <v>4.687671407499835</v>
       </c>
       <c r="H497" t="n">
         <v>8.300000000000001</v>
@@ -14823,7 +14823,7 @@
         <v>4.503137460422939</v>
       </c>
       <c r="G498" t="n">
-        <v>4.684905154006945</v>
+        <v>4.685828089005546</v>
       </c>
       <c r="H498" t="n">
         <v>8.4</v>
@@ -14856,7 +14856,7 @@
         <v>4.471638793363569</v>
       </c>
       <c r="G499" t="n">
-        <v>4.688591794127164</v>
+        <v>4.690430029938915</v>
       </c>
       <c r="H499" t="n">
         <v>8.300000000000001</v>
@@ -14887,7 +14887,7 @@
         <v>4.472780997942346</v>
       </c>
       <c r="G500" t="n">
-        <v>4.697749367281185</v>
+        <v>4.69866052907543</v>
       </c>
       <c r="H500" t="n">
         <v>8.300000000000001</v>
@@ -14913,7 +14913,9 @@
       </c>
       <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr"/>
-      <c r="G501" t="inlineStr"/>
+      <c r="G501" t="n">
+        <v>4.687671407499835</v>
+      </c>
       <c r="H501" t="inlineStr"/>
       <c r="I501" t="n">
         <v>4.642080540008188</v>
@@ -14928,7 +14930,9 @@
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
-      <c r="C502" t="inlineStr"/>
+      <c r="C502" t="n">
+        <v>2.6350455</v>
+      </c>
       <c r="D502" t="n">
         <v>4.566429357671661</v>
       </c>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -5960,7 +5960,7 @@
         <v>4.11414718951828</v>
       </c>
       <c r="H218" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I218" t="n">
         <v>4.186467851097906</v>
@@ -6119,7 +6119,7 @@
         <v>4.110873864173311</v>
       </c>
       <c r="H223" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I223" t="n">
         <v>4.198103796512953</v>
@@ -6214,7 +6214,7 @@
         <v>4.131961425793407</v>
       </c>
       <c r="H226" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I226" t="n">
         <v>4.203796695783181</v>
@@ -6466,7 +6466,7 @@
         <v>4.141546163706395</v>
       </c>
       <c r="H234" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I234" t="n">
         <v>4.224202549480315</v>
@@ -7891,7 +7891,7 @@
         <v>4.264087336809195</v>
       </c>
       <c r="H279" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I279" t="n">
         <v>4.294287720365875</v>
@@ -9159,7 +9159,7 @@
         <v>4.333361462692601</v>
       </c>
       <c r="H319" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I319" t="n">
         <v>4.349890764643811</v>
@@ -10235,7 +10235,7 @@
         <v>4.383275854074314</v>
       </c>
       <c r="H353" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I353" t="n">
         <v>4.388381400311889</v>
@@ -10266,7 +10266,7 @@
         <v>4.382026634673881</v>
       </c>
       <c r="H354" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I354" t="n">
         <v>4.388753955423308</v>
@@ -10394,7 +10394,7 @@
         <v>4.394449154672439</v>
       </c>
       <c r="H358" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="I358" t="n">
         <v>4.385395952143486</v>
@@ -10456,7 +10456,7 @@
         <v>4.394449154672439</v>
       </c>
       <c r="H360" t="n">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="I360" t="n">
         <v>4.38414938005486</v>
@@ -10551,7 +10551,7 @@
         <v>4.406719247264253</v>
       </c>
       <c r="H363" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="I363" t="n">
         <v>4.380775852772229</v>
@@ -10869,7 +10869,7 @@
         <v>4.449685283147696</v>
       </c>
       <c r="H373" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="I373" t="n">
         <v>4.387511564904451</v>
@@ -11059,7 +11059,7 @@
         <v>4.447346100794524</v>
       </c>
       <c r="H379" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="I379" t="n">
         <v>4.3945726038424</v>
@@ -11280,7 +11280,7 @@
         <v>4.472780997942346</v>
       </c>
       <c r="H386" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I386" t="n">
         <v>4.392348183745753</v>
@@ -11375,7 +11375,7 @@
         <v>4.478472532942134</v>
       </c>
       <c r="H389" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I389" t="n">
         <v>4.402196841463264</v>
@@ -11406,7 +11406,7 @@
         <v>4.489759334476764</v>
       </c>
       <c r="H390" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I390" t="n">
         <v>4.402441819416474</v>
@@ -11501,7 +11501,7 @@
         <v>4.478472532942134</v>
       </c>
       <c r="H393" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="I393" t="n">
         <v>4.403788126455394</v>
@@ -11629,7 +11629,7 @@
         <v>4.513054897080286</v>
       </c>
       <c r="H397" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I397" t="n">
         <v>4.407938016458383</v>
@@ -11660,7 +11660,7 @@
         <v>4.505349850705881</v>
       </c>
       <c r="H398" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I398" t="n">
         <v>4.406963119963913</v>
@@ -11819,7 +11819,7 @@
         <v>4.51852237926242</v>
       </c>
       <c r="H403" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I403" t="n">
         <v>4.425205848767815</v>
@@ -11976,7 +11976,7 @@
         <v>4.522874943261261</v>
       </c>
       <c r="H408" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I408" t="n">
         <v>4.425804257019769</v>
@@ -12071,7 +12071,7 @@
         <v>4.536891345234797</v>
       </c>
       <c r="H411" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I411" t="n">
         <v>4.42232849394725</v>
@@ -12135,7 +12135,7 @@
         <v>4.539030383483547</v>
       </c>
       <c r="H413" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I413" t="n">
         <v>4.434619084793052</v>
@@ -12389,7 +12389,7 @@
         <v>4.551769409260976</v>
       </c>
       <c r="H421" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I421" t="n">
         <v>4.442768896629268</v>
@@ -12420,7 +12420,7 @@
         <v>4.557029810660157</v>
       </c>
       <c r="H422" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I422" t="n">
         <v>4.437697832044343</v>
@@ -12451,7 +12451,7 @@
         <v>4.552823705615882</v>
       </c>
       <c r="H423" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I423" t="n">
         <v>4.437934266612178</v>
@@ -12546,7 +12546,7 @@
         <v>4.485259889315534</v>
       </c>
       <c r="H426" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I426" t="n">
         <v>4.440059665924491</v>
@@ -12769,7 +12769,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="H433" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I433" t="n">
         <v>4.442533602510535</v>
@@ -13054,7 +13054,7 @@
         <v>4.621043535144381</v>
       </c>
       <c r="H442" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I442" t="n">
         <v>4.465103197090973</v>
@@ -13085,7 +13085,7 @@
         <v>4.632785353021065</v>
       </c>
       <c r="H443" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I443" t="n">
         <v>4.469465003822716</v>
@@ -13116,7 +13116,7 @@
         <v>4.634728988229636</v>
       </c>
       <c r="H444" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I444" t="n">
         <v>4.473579765600494</v>
@@ -13211,7 +13211,7 @@
         <v>4.636668853047462</v>
       </c>
       <c r="H447" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I447" t="n">
         <v>4.486386649998124</v>
@@ -13244,7 +13244,7 @@
         <v>4.639571612705423</v>
       </c>
       <c r="H448" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I448" t="n">
         <v>4.50225113198025</v>
@@ -13275,7 +13275,7 @@
         <v>4.643428898105181</v>
       </c>
       <c r="H449" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I449" t="n">
         <v>4.506895616719751</v>
@@ -13401,7 +13401,7 @@
         <v>4.632785353021065</v>
       </c>
       <c r="H453" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I453" t="n">
         <v>4.530554392607302</v>
@@ -13496,7 +13496,7 @@
         <v>4.624972813284271</v>
       </c>
       <c r="H456" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I456" t="n">
         <v>4.542017370982823</v>
@@ -13781,7 +13781,7 @@
         <v>4.604169685654508</v>
       </c>
       <c r="H465" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I465" t="n">
         <v>4.586293130218402</v>
@@ -13814,7 +13814,7 @@
         <v>4.614129927359564</v>
       </c>
       <c r="H466" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I466" t="n">
         <v>4.580570069119859</v>
@@ -13909,7 +13909,7 @@
         <v>4.623991940228679</v>
       </c>
       <c r="H469" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="I469" t="n">
         <v>4.581287245524759</v>
@@ -14916,7 +14916,9 @@
       <c r="G501" t="n">
         <v>4.687671407499835</v>
       </c>
-      <c r="H501" t="inlineStr"/>
+      <c r="H501" t="n">
+        <v>8.199999999999999</v>
+      </c>
       <c r="I501" t="n">
         <v>4.642080540008188</v>
       </c>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -14942,7 +14942,9 @@
       <c r="F502" t="inlineStr"/>
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
-      <c r="I502" t="inlineStr"/>
+      <c r="I502" t="n">
+        <v>4.638508245598602</v>
+      </c>
       <c r="J502" t="inlineStr"/>
       <c r="K502" t="inlineStr"/>
     </row>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -11430,7 +11430,7 @@
         <v>4.678420647727684</v>
       </c>
       <c r="E391" t="n">
-        <v>4.652053771886941</v>
+        <v>4.653007515402251</v>
       </c>
       <c r="F391" t="n">
         <v>4.74493212836325</v>
@@ -11620,7 +11620,7 @@
         <v>4.730039168033961</v>
       </c>
       <c r="E397" t="n">
-        <v>4.686750172980514</v>
+        <v>4.687671407499835</v>
       </c>
       <c r="F397" t="n">
         <v>4.772378104971998</v>
@@ -11813,7 +11813,7 @@
         <v>4.670957926526095</v>
       </c>
       <c r="F403" t="n">
-        <v>4.719391330078114</v>
+        <v>4.720282993088596</v>
       </c>
       <c r="G403" t="n">
         <v>4.51852237926242</v>
@@ -11936,7 +11936,7 @@
         <v>4.635699391022914</v>
       </c>
       <c r="E407" t="n">
-        <v>4.671893818030999</v>
+        <v>4.670957926526095</v>
       </c>
       <c r="F407" t="n">
         <v>4.725616339063959</v>
@@ -12000,7 +12000,7 @@
         <v>4.60816569496789</v>
       </c>
       <c r="E409" t="n">
-        <v>4.670021158307708</v>
+        <v>4.670957926526095</v>
       </c>
       <c r="F409" t="n">
         <v>4.747537427275013</v>
@@ -12157,7 +12157,7 @@
         <v>4.671893818030999</v>
       </c>
       <c r="E414" t="n">
-        <v>4.694096395182493</v>
+        <v>4.695010889987881</v>
       </c>
       <c r="F414" t="n">
         <v>4.722063937459591</v>
@@ -12255,7 +12255,7 @@
         <v>4.657762636107262</v>
       </c>
       <c r="F417" t="n">
-        <v>4.703203926259457</v>
+        <v>4.702296896718814</v>
       </c>
       <c r="G417" t="n">
         <v>4.550714000192032</v>
@@ -12475,7 +12475,7 @@
         <v>4.590056548178043</v>
       </c>
       <c r="E424" t="n">
-        <v>4.464758032271346</v>
+        <v>4.463606621666305</v>
       </c>
       <c r="F424" t="n">
         <v>4.247065649239764</v>
@@ -13015,7 +13015,7 @@
         <v>4.606169686321175</v>
       </c>
       <c r="F441" t="n">
-        <v>4.58700621536042</v>
+        <v>4.585987366571318</v>
       </c>
       <c r="G441" t="n">
         <v>4.620058798481842</v>
@@ -13235,7 +13235,7 @@
         <v>4.651099117876491</v>
       </c>
       <c r="E448" t="n">
-        <v>4.606169686321175</v>
+        <v>4.605170185988092</v>
       </c>
       <c r="F448" t="n">
         <v>4.570578741218473</v>
@@ -13364,7 +13364,7 @@
         <v>4.603168183317418</v>
       </c>
       <c r="F452" t="n">
-        <v>4.540098189244376</v>
+        <v>4.541164856012179</v>
       </c>
       <c r="G452" t="n">
         <v>4.622027303054514</v>
@@ -13395,7 +13395,7 @@
         <v>4.629862798578463</v>
       </c>
       <c r="F453" t="n">
-        <v>4.56954300834494</v>
+        <v>4.5685062016165</v>
       </c>
       <c r="G453" t="n">
         <v>4.632785353021065</v>
@@ -13456,7 +13456,7 @@
         <v>4.572646994282532</v>
       </c>
       <c r="E455" t="n">
-        <v>4.602165676967792</v>
+        <v>4.603168183317418</v>
       </c>
       <c r="F455" t="n">
         <v>4.5685062016165</v>
@@ -13585,7 +13585,7 @@
         <v>4.623991940228679</v>
       </c>
       <c r="F459" t="n">
-        <v>4.600157644164547</v>
+        <v>4.601162164590552</v>
       </c>
       <c r="G459" t="n">
         <v>4.622027303054514</v>
@@ -13618,7 +13618,7 @@
         <v>4.61015772749913</v>
       </c>
       <c r="F460" t="n">
-        <v>4.592084946439436</v>
+        <v>4.593097604753822</v>
       </c>
       <c r="G460" t="n">
         <v>4.618086411254637</v>
@@ -13680,7 +13680,7 @@
         <v>4.633757642840004</v>
       </c>
       <c r="F462" t="n">
-        <v>4.613138355637268</v>
+        <v>4.614129927359564</v>
       </c>
       <c r="G462" t="n">
         <v>4.614129927359564</v>
@@ -13710,7 +13710,7 @@
         <v>4.584967478670572</v>
       </c>
       <c r="E463" t="n">
-        <v>4.622027303054514</v>
+        <v>4.621043535144381</v>
       </c>
       <c r="F463" t="n">
         <v>4.600157644164547</v>
@@ -13741,7 +13741,7 @@
         <v>4.559126247486684</v>
       </c>
       <c r="E464" t="n">
-        <v>4.620058798481842</v>
+        <v>4.621043535144381</v>
       </c>
       <c r="F464" t="n">
         <v>4.604169685654508</v>
@@ -13772,10 +13772,10 @@
         <v>4.541164856012179</v>
       </c>
       <c r="E465" t="n">
-        <v>4.619073091157083</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="F465" t="n">
-        <v>4.584967478670572</v>
+        <v>4.581901559048737</v>
       </c>
       <c r="G465" t="n">
         <v>4.604169685654508</v>
@@ -13931,7 +13931,7 @@
         <v>4.583946549536464</v>
       </c>
       <c r="E470" t="n">
-        <v>4.623991940228679</v>
+        <v>4.623010104116422</v>
       </c>
       <c r="F470" t="n">
         <v>4.598145571051127</v>
@@ -13962,7 +13962,7 @@
         <v>4.581901559048737</v>
       </c>
       <c r="E471" t="n">
-        <v>4.629862798578463</v>
+        <v>4.628886712605407</v>
       </c>
       <c r="F471" t="n">
         <v>4.560172820057356</v>
@@ -14029,7 +14029,7 @@
         <v>4.631812116934513</v>
       </c>
       <c r="F473" t="n">
-        <v>4.559126247486684</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="G473" t="n">
         <v>4.631812116934513</v>
@@ -14057,10 +14057,10 @@
         <v>4.597138014290827</v>
       </c>
       <c r="E474" t="n">
-        <v>4.620058798481842</v>
+        <v>4.619073091157083</v>
       </c>
       <c r="F474" t="n">
-        <v>4.546481189639412</v>
+        <v>4.547541073151455</v>
       </c>
       <c r="G474" t="n">
         <v>4.630837932736669</v>
@@ -14090,10 +14090,10 @@
         <v>4.588024027153121</v>
       </c>
       <c r="E475" t="n">
-        <v>4.621043535144381</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="F475" t="n">
-        <v>4.574710978503383</v>
+        <v>4.575741375297279</v>
       </c>
       <c r="G475" t="n">
         <v>4.624972813284271</v>
@@ -14152,10 +14152,10 @@
         <v>4.596129441335942</v>
       </c>
       <c r="E477" t="n">
-        <v>4.628886712605407</v>
+        <v>4.629862798578463</v>
       </c>
       <c r="F477" t="n">
-        <v>4.542230386214217</v>
+        <v>4.537961436294641</v>
       </c>
       <c r="G477" t="n">
         <v>4.65681341913993</v>
@@ -14216,7 +14216,7 @@
         <v>4.541164856012179</v>
       </c>
       <c r="E479" t="n">
-        <v>4.619073091157083</v>
+        <v>4.620058798481842</v>
       </c>
       <c r="F479" t="n">
         <v>4.52178857704904</v>
@@ -14280,7 +14280,7 @@
         <v>4.530446639792155</v>
       </c>
       <c r="E481" t="n">
-        <v>4.617098756853365</v>
+        <v>4.618086411254637</v>
       </c>
       <c r="F481" t="n">
         <v>4.55597994179732</v>
@@ -14378,7 +14378,7 @@
         <v>4.627909672957581</v>
       </c>
       <c r="F484" t="n">
-        <v>4.525044141508807</v>
+        <v>4.526126978647638</v>
       </c>
       <c r="G484" t="n">
         <v>4.65681341913993</v>
@@ -14406,10 +14406,10 @@
         <v>4.576770711466393</v>
       </c>
       <c r="E485" t="n">
-        <v>4.613138355637268</v>
+        <v>4.612145799724517</v>
       </c>
       <c r="F485" t="n">
-        <v>4.519612297626445</v>
+        <v>4.520701029361642</v>
       </c>
       <c r="G485" t="n">
         <v>4.665324108807838</v>
@@ -14440,7 +14440,7 @@
         <v>4.60816569496789</v>
       </c>
       <c r="F486" t="n">
-        <v>4.51085950651685</v>
+        <v>4.511957804265912</v>
       </c>
       <c r="G486" t="n">
         <v>4.663439094112067</v>
@@ -14470,7 +14470,7 @@
         <v>4.504244267398131</v>
       </c>
       <c r="E487" t="n">
-        <v>4.640537329825382</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F487" t="n">
         <v>4.52178857704904</v>
@@ -14501,7 +14501,7 @@
         <v>4.529368472571809</v>
       </c>
       <c r="E488" t="n">
-        <v>4.641502115235482</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F488" t="n">
         <v>4.526126978647638</v>
@@ -14532,10 +14532,10 @@
         <v>4.529368472571809</v>
       </c>
       <c r="E489" t="n">
-        <v>4.626931677769604</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="F489" t="n">
-        <v>4.535820107853298</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="G489" t="n">
         <v>4.671893818030999</v>
@@ -14596,7 +14596,7 @@
         <v>4.551769409260976</v>
       </c>
       <c r="E491" t="n">
-        <v>4.637637376125593</v>
+        <v>4.638604962074329</v>
       </c>
       <c r="F491" t="n">
         <v>4.51085950651685</v>
@@ -14627,7 +14627,7 @@
         <v>4.557029810660157</v>
       </c>
       <c r="E492" t="n">
-        <v>4.638604962074329</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F492" t="n">
         <v>4.502029427068578</v>
@@ -14660,10 +14660,10 @@
         <v>4.547541073151455</v>
       </c>
       <c r="E493" t="n">
-        <v>4.632785353021065</v>
+        <v>4.633757642840004</v>
       </c>
       <c r="F493" t="n">
-        <v>4.517431271680085</v>
+        <v>4.51852237926242</v>
       </c>
       <c r="G493" t="n">
         <v>4.681204872264089</v>
@@ -14691,7 +14691,7 @@
         <v>4.61512051684126</v>
       </c>
       <c r="E494" t="n">
-        <v>4.633757642840004</v>
+        <v>4.632785353021065</v>
       </c>
       <c r="F494" t="n">
         <v>4.507557357121091</v>
@@ -14722,7 +14722,7 @@
         <v>4.59511985013459</v>
       </c>
       <c r="E495" t="n">
-        <v>4.626931677769604</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="F495" t="n">
         <v>4.49423862528081</v>
@@ -14755,10 +14755,10 @@
         <v>4.561218298458908</v>
       </c>
       <c r="E496" t="n">
-        <v>4.640537329825382</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F496" t="n">
-        <v>4.490881039585964</v>
+        <v>4.492001487882454</v>
       </c>
       <c r="G496" t="n">
         <v>4.68213122712422</v>
@@ -14786,10 +14786,10 @@
         <v>4.531523645819793</v>
       </c>
       <c r="E497" t="n">
-        <v>4.640537329825382</v>
+        <v>4.639571612705423</v>
       </c>
       <c r="F497" t="n">
-        <v>4.489759334476764</v>
+        <v>4.490881039585964</v>
       </c>
       <c r="G497" t="n">
         <v>4.687671407499835</v>
@@ -14817,10 +14817,10 @@
         <v>4.546481189639412</v>
       </c>
       <c r="E498" t="n">
-        <v>4.640537329825382</v>
+        <v>4.638604962074329</v>
       </c>
       <c r="F498" t="n">
-        <v>4.503137460422939</v>
+        <v>4.504244267398131</v>
       </c>
       <c r="G498" t="n">
         <v>4.685828089005546</v>
@@ -14850,10 +14850,10 @@
         <v>4.540098189244376</v>
       </c>
       <c r="E499" t="n">
-        <v>4.639571612705423</v>
+        <v>4.638604962074329</v>
       </c>
       <c r="F499" t="n">
-        <v>4.471638793363569</v>
+        <v>4.472780997942346</v>
       </c>
       <c r="G499" t="n">
         <v>4.690430029938915</v>
@@ -14881,7 +14881,7 @@
         <v>4.563305981889393</v>
       </c>
       <c r="E500" t="n">
-        <v>4.635699391022914</v>
+        <v>4.631812116934513</v>
       </c>
       <c r="F500" t="n">
         <v>4.472780997942346</v>
@@ -14911,8 +14911,12 @@
       <c r="D501" t="n">
         <v>4.583946549536464</v>
       </c>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
+      <c r="E501" t="n">
+        <v>4.628886712605407</v>
+      </c>
+      <c r="F501" t="n">
+        <v>4.479606963012746</v>
+      </c>
       <c r="G501" t="n">
         <v>4.687671407499835</v>
       </c>
@@ -14945,7 +14949,9 @@
       <c r="I502" t="n">
         <v>4.638508245598602</v>
       </c>
-      <c r="J502" t="inlineStr"/>
+      <c r="J502" t="n">
+        <v>4.596689494135473</v>
+      </c>
       <c r="K502" t="inlineStr"/>
     </row>
   </sheetData>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,16 +20,13 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,24 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -435,64 +421,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -511,7 +497,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -530,7 +516,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="n">
@@ -551,7 +537,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -570,7 +556,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -589,7 +575,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="n">
@@ -610,7 +596,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -629,7 +615,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="1" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -648,7 +634,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="1" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="n">
@@ -669,7 +655,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="1" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -688,7 +674,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="1" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -707,7 +693,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="1" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="n">
@@ -728,7 +714,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="1" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -747,7 +733,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="1" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -766,7 +752,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="1" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="n">
@@ -787,7 +773,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="1" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -806,7 +792,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="1" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -825,7 +811,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="1" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="n">
@@ -846,7 +832,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="1" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -865,7 +851,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="1" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -884,7 +870,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="1" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="n">
@@ -905,7 +891,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="1" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -924,7 +910,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="1" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -943,7 +929,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="1" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="n">
@@ -964,7 +950,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="n">
+      <c r="A26" s="1" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -983,7 +969,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n">
+      <c r="A27" s="1" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1002,7 +988,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="n">
+      <c r="A28" s="1" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="n">
@@ -1023,7 +1009,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n">
+      <c r="A29" s="1" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1042,7 +1028,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="n">
+      <c r="A30" s="1" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1061,7 +1047,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="n">
+      <c r="A31" s="1" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="n">
@@ -1082,7 +1068,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n">
+      <c r="A32" s="1" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1101,7 +1087,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="n">
+      <c r="A33" s="1" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1120,7 +1106,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="n">
+      <c r="A34" s="1" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="n">
@@ -1141,7 +1127,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="n">
+      <c r="A35" s="1" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1160,7 +1146,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="n">
+      <c r="A36" s="1" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1179,7 +1165,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n">
+      <c r="A37" s="1" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="n">
@@ -1200,7 +1186,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="n">
+      <c r="A38" s="1" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1219,7 +1205,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n">
+      <c r="A39" s="1" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1238,7 +1224,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="n">
+      <c r="A40" s="1" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="n">
@@ -1259,7 +1245,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="n">
+      <c r="A41" s="1" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1278,7 +1264,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="n">
+      <c r="A42" s="1" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1297,7 +1283,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="n">
+      <c r="A43" s="1" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="n">
@@ -1318,7 +1304,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="n">
+      <c r="A44" s="1" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1337,7 +1323,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="n">
+      <c r="A45" s="1" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1356,7 +1342,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="n">
+      <c r="A46" s="1" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="n">
@@ -1377,7 +1363,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="n">
+      <c r="A47" s="1" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1396,7 +1382,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="n">
+      <c r="A48" s="1" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1415,7 +1401,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="n">
+      <c r="A49" s="1" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="n">
@@ -1436,7 +1422,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="n">
+      <c r="A50" s="1" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1455,7 +1441,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="n">
+      <c r="A51" s="1" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1474,7 +1460,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="n">
+      <c r="A52" s="1" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="n">
@@ -1495,7 +1481,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="n">
+      <c r="A53" s="1" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1514,7 +1500,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="n">
+      <c r="A54" s="1" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1533,7 +1519,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="n">
+      <c r="A55" s="1" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="n">
@@ -1554,7 +1540,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="n">
+      <c r="A56" s="1" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1573,7 +1559,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="n">
+      <c r="A57" s="1" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1592,7 +1578,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="n">
+      <c r="A58" s="1" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="n">
@@ -1613,7 +1599,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="n">
+      <c r="A59" s="1" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1632,7 +1618,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="n">
+      <c r="A60" s="1" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1651,7 +1637,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="n">
+      <c r="A61" s="1" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="n">
@@ -1672,7 +1658,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="n">
+      <c r="A62" s="1" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1695,7 +1681,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="n">
+      <c r="A63" s="1" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1718,7 +1704,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="n">
+      <c r="A64" s="1" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="n">
@@ -1743,7 +1729,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="n">
+      <c r="A65" s="1" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1766,7 +1752,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="n">
+      <c r="A66" s="1" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1789,7 +1775,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="n">
+      <c r="A67" s="1" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="n">
@@ -1814,7 +1800,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="n">
+      <c r="A68" s="1" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1837,7 +1823,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="n">
+      <c r="A69" s="1" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1860,7 +1846,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="n">
+      <c r="A70" s="1" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="n">
@@ -1885,7 +1871,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="n">
+      <c r="A71" s="1" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1908,7 +1894,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="n">
+      <c r="A72" s="1" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1931,7 +1917,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="n">
+      <c r="A73" s="1" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="n">
@@ -1956,7 +1942,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="n">
+      <c r="A74" s="1" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1979,7 +1965,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="n">
+      <c r="A75" s="1" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2002,7 +1988,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="n">
+      <c r="A76" s="1" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="n">
@@ -2027,7 +2013,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="n">
+      <c r="A77" s="1" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2050,7 +2036,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="n">
+      <c r="A78" s="1" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2073,7 +2059,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="n">
+      <c r="A79" s="1" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="n">
@@ -2098,7 +2084,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="n">
+      <c r="A80" s="1" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2121,7 +2107,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="n">
+      <c r="A81" s="1" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2144,7 +2130,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
+      <c r="A82" s="1" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="n">
@@ -2169,7 +2155,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
+      <c r="A83" s="1" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2192,7 +2178,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
+      <c r="A84" s="1" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2215,7 +2201,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
+      <c r="A85" s="1" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="n">
@@ -2240,7 +2226,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="n">
+      <c r="A86" s="1" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2263,7 +2249,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="n">
+      <c r="A87" s="1" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2286,7 +2272,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="n">
+      <c r="A88" s="1" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="n">
@@ -2311,7 +2297,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="n">
+      <c r="A89" s="1" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2334,7 +2320,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="n">
+      <c r="A90" s="1" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2357,7 +2343,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="n">
+      <c r="A91" s="1" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="n">
@@ -2382,7 +2368,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="n">
+      <c r="A92" s="1" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2405,7 +2391,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="n">
+      <c r="A93" s="1" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2428,7 +2414,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="n">
+      <c r="A94" s="1" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="n">
@@ -2453,7 +2439,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="n">
+      <c r="A95" s="1" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2476,7 +2462,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="n">
+      <c r="A96" s="1" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2499,7 +2485,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="n">
+      <c r="A97" s="1" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="n">
@@ -2524,7 +2510,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="n">
+      <c r="A98" s="1" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2547,7 +2533,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="n">
+      <c r="A99" s="1" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2570,7 +2556,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="n">
+      <c r="A100" s="1" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="n">
@@ -2595,7 +2581,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="n">
+      <c r="A101" s="1" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2618,7 +2604,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="n">
+      <c r="A102" s="1" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2641,7 +2627,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="n">
+      <c r="A103" s="1" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="n">
@@ -2666,7 +2652,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="n">
+      <c r="A104" s="1" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2689,7 +2675,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="n">
+      <c r="A105" s="1" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2712,7 +2698,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="n">
+      <c r="A106" s="1" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="n">
@@ -2737,7 +2723,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="n">
+      <c r="A107" s="1" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2760,7 +2746,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="n">
+      <c r="A108" s="1" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2783,7 +2769,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="n">
+      <c r="A109" s="1" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="n">
@@ -2808,7 +2794,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="n">
+      <c r="A110" s="1" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2833,7 +2819,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="n">
+      <c r="A111" s="1" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2858,7 +2844,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="n">
+      <c r="A112" s="1" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="n">
@@ -2885,7 +2871,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="n">
+      <c r="A113" s="1" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2910,7 +2896,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="n">
+      <c r="A114" s="1" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2935,7 +2921,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="n">
+      <c r="A115" s="1" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="n">
@@ -2962,7 +2948,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="n">
+      <c r="A116" s="1" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2987,7 +2973,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="n">
+      <c r="A117" s="1" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -3012,7 +2998,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="n">
+      <c r="A118" s="1" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="n">
@@ -3039,7 +3025,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="n">
+      <c r="A119" s="1" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3064,7 +3050,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="n">
+      <c r="A120" s="1" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3089,7 +3075,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="n">
+      <c r="A121" s="1" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="n">
@@ -3116,7 +3102,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="n">
+      <c r="A122" s="1" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -3141,7 +3127,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="n">
+      <c r="A123" s="1" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -3166,7 +3152,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="n">
+      <c r="A124" s="1" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -3193,7 +3179,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="n">
+      <c r="A125" s="1" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -3218,7 +3204,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="n">
+      <c r="A126" s="1" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -3243,7 +3229,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="n">
+      <c r="A127" s="1" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -3270,7 +3256,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="n">
+      <c r="A128" s="1" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -3295,7 +3281,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="n">
+      <c r="A129" s="1" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -3320,7 +3306,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="n">
+      <c r="A130" s="1" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -3347,7 +3333,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="n">
+      <c r="A131" s="1" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3372,7 +3358,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="n">
+      <c r="A132" s="1" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3397,7 +3383,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="n">
+      <c r="A133" s="1" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -3424,7 +3410,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="n">
+      <c r="A134" s="1" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3451,7 +3437,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="n">
+      <c r="A135" s="1" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3478,7 +3464,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="n">
+      <c r="A136" s="1" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3507,7 +3493,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="n">
+      <c r="A137" s="1" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3534,7 +3520,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="n">
+      <c r="A138" s="1" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3561,7 +3547,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="n">
+      <c r="A139" s="1" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3590,7 +3576,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="n">
+      <c r="A140" s="1" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3617,7 +3603,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="n">
+      <c r="A141" s="1" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3644,7 +3630,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="n">
+      <c r="A142" s="1" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3673,7 +3659,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="n">
+      <c r="A143" s="1" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3700,7 +3686,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="n">
+      <c r="A144" s="1" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3727,7 +3713,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="n">
+      <c r="A145" s="1" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3756,7 +3742,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="n">
+      <c r="A146" s="1" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3783,7 +3769,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="n">
+      <c r="A147" s="1" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3810,7 +3796,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="n">
+      <c r="A148" s="1" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3839,7 +3825,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="n">
+      <c r="A149" s="1" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3866,7 +3852,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="n">
+      <c r="A150" s="1" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3893,7 +3879,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="n">
+      <c r="A151" s="1" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3922,7 +3908,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="n">
+      <c r="A152" s="1" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3949,7 +3935,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="n">
+      <c r="A153" s="1" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3976,7 +3962,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="n">
+      <c r="A154" s="1" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -4005,7 +3991,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="n">
+      <c r="A155" s="1" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -4032,7 +4018,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="n">
+      <c r="A156" s="1" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -4059,7 +4045,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="n">
+      <c r="A157" s="1" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -4088,7 +4074,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="n">
+      <c r="A158" s="1" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -4115,7 +4101,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="n">
+      <c r="A159" s="1" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -4142,7 +4128,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="n">
+      <c r="A160" s="1" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -4171,7 +4157,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="n">
+      <c r="A161" s="1" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -4198,7 +4184,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="n">
+      <c r="A162" s="1" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -4225,7 +4211,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="n">
+      <c r="A163" s="1" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -4254,7 +4240,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="n">
+      <c r="A164" s="1" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -4281,7 +4267,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="n">
+      <c r="A165" s="1" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -4308,7 +4294,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="n">
+      <c r="A166" s="1" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -4337,7 +4323,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="n">
+      <c r="A167" s="1" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -4364,7 +4350,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="n">
+      <c r="A168" s="1" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -4391,7 +4377,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="n">
+      <c r="A169" s="1" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -4420,7 +4406,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="n">
+      <c r="A170" s="1" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -4451,7 +4437,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="n">
+      <c r="A171" s="1" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4482,7 +4468,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="n">
+      <c r="A172" s="1" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -4515,7 +4501,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="n">
+      <c r="A173" s="1" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4546,7 +4532,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="n">
+      <c r="A174" s="1" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4577,7 +4563,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="n">
+      <c r="A175" s="1" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -4610,7 +4596,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="n">
+      <c r="A176" s="1" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4641,7 +4627,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="n">
+      <c r="A177" s="1" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4672,7 +4658,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="n">
+      <c r="A178" s="1" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4705,7 +4691,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="n">
+      <c r="A179" s="1" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4736,7 +4722,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="n">
+      <c r="A180" s="1" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4767,7 +4753,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="n">
+      <c r="A181" s="1" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4800,7 +4786,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="n">
+      <c r="A182" s="1" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4831,7 +4817,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="n">
+      <c r="A183" s="1" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4862,7 +4848,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="n">
+      <c r="A184" s="1" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4895,7 +4881,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="n">
+      <c r="A185" s="1" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4926,7 +4912,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="n">
+      <c r="A186" s="1" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4957,7 +4943,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="n">
+      <c r="A187" s="1" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4990,7 +4976,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="n">
+      <c r="A188" s="1" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -5021,7 +5007,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="n">
+      <c r="A189" s="1" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -5052,7 +5038,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="n">
+      <c r="A190" s="1" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -5085,7 +5071,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="n">
+      <c r="A191" s="1" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -5116,7 +5102,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="n">
+      <c r="A192" s="1" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -5147,7 +5133,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="n">
+      <c r="A193" s="1" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -5180,7 +5166,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="n">
+      <c r="A194" s="1" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -5211,7 +5197,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="n">
+      <c r="A195" s="1" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -5242,7 +5228,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="n">
+      <c r="A196" s="1" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -5275,7 +5261,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="n">
+      <c r="A197" s="1" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -5306,7 +5292,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="n">
+      <c r="A198" s="1" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -5337,7 +5323,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="n">
+      <c r="A199" s="1" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -5370,7 +5356,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="n">
+      <c r="A200" s="1" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -5401,7 +5387,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="2" t="n">
+      <c r="A201" s="1" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -5432,7 +5418,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="2" t="n">
+      <c r="A202" s="1" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -5465,7 +5451,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="2" t="n">
+      <c r="A203" s="1" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -5496,7 +5482,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="2" t="n">
+      <c r="A204" s="1" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -5527,7 +5513,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="2" t="n">
+      <c r="A205" s="1" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -5560,7 +5546,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="n">
+      <c r="A206" s="1" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -5591,7 +5577,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="2" t="n">
+      <c r="A207" s="1" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -5622,7 +5608,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="2" t="n">
+      <c r="A208" s="1" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -5655,7 +5641,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="2" t="n">
+      <c r="A209" s="1" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -5686,7 +5672,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="2" t="n">
+      <c r="A210" s="1" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5717,7 +5703,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="2" t="n">
+      <c r="A211" s="1" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5750,7 +5736,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="2" t="n">
+      <c r="A212" s="1" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5781,7 +5767,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="2" t="n">
+      <c r="A213" s="1" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5812,7 +5798,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="2" t="n">
+      <c r="A214" s="1" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5845,7 +5831,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="2" t="n">
+      <c r="A215" s="1" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5876,7 +5862,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="2" t="n">
+      <c r="A216" s="1" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5907,7 +5893,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="2" t="n">
+      <c r="A217" s="1" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5940,7 +5926,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="2" t="n">
+      <c r="A218" s="1" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5971,7 +5957,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="2" t="n">
+      <c r="A219" s="1" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -6002,7 +5988,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="2" t="n">
+      <c r="A220" s="1" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -6035,7 +6021,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="2" t="n">
+      <c r="A221" s="1" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -6066,7 +6052,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="2" t="n">
+      <c r="A222" s="1" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -6097,7 +6083,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="2" t="n">
+      <c r="A223" s="1" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -6130,7 +6116,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="2" t="n">
+      <c r="A224" s="1" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -6161,7 +6147,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="2" t="n">
+      <c r="A225" s="1" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -6192,7 +6178,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="2" t="n">
+      <c r="A226" s="1" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -6225,7 +6211,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="2" t="n">
+      <c r="A227" s="1" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -6256,7 +6242,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="2" t="n">
+      <c r="A228" s="1" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -6287,7 +6273,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="2" t="n">
+      <c r="A229" s="1" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -6320,7 +6306,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="2" t="n">
+      <c r="A230" s="1" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -6351,7 +6337,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="2" t="n">
+      <c r="A231" s="1" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -6382,7 +6368,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="2" t="n">
+      <c r="A232" s="1" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -6415,7 +6401,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="2" t="n">
+      <c r="A233" s="1" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -6446,7 +6432,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="2" t="n">
+      <c r="A234" s="1" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -6477,7 +6463,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="2" t="n">
+      <c r="A235" s="1" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -6510,7 +6496,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="2" t="n">
+      <c r="A236" s="1" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -6541,7 +6527,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="2" t="n">
+      <c r="A237" s="1" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -6572,7 +6558,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="2" t="n">
+      <c r="A238" s="1" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -6605,7 +6591,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="2" t="n">
+      <c r="A239" s="1" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -6636,7 +6622,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="2" t="n">
+      <c r="A240" s="1" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -6667,7 +6653,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="2" t="n">
+      <c r="A241" s="1" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -6700,7 +6686,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="2" t="n">
+      <c r="A242" s="1" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6731,7 +6717,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="2" t="n">
+      <c r="A243" s="1" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6762,7 +6748,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="2" t="n">
+      <c r="A244" s="1" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6795,7 +6781,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="2" t="n">
+      <c r="A245" s="1" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6826,7 +6812,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="2" t="n">
+      <c r="A246" s="1" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6857,7 +6843,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="2" t="n">
+      <c r="A247" s="1" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6890,7 +6876,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="2" t="n">
+      <c r="A248" s="1" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6921,7 +6907,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="2" t="n">
+      <c r="A249" s="1" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6952,7 +6938,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="2" t="n">
+      <c r="A250" s="1" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6985,7 +6971,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="2" t="n">
+      <c r="A251" s="1" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7016,7 +7002,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="2" t="n">
+      <c r="A252" s="1" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -7047,7 +7033,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="2" t="n">
+      <c r="A253" s="1" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -7080,7 +7066,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="2" t="n">
+      <c r="A254" s="1" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -7111,7 +7097,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="2" t="n">
+      <c r="A255" s="1" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -7142,7 +7128,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="2" t="n">
+      <c r="A256" s="1" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -7175,7 +7161,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="2" t="n">
+      <c r="A257" s="1" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -7206,7 +7192,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="2" t="n">
+      <c r="A258" s="1" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -7237,7 +7223,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="2" t="n">
+      <c r="A259" s="1" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -7270,7 +7256,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="2" t="n">
+      <c r="A260" s="1" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -7301,7 +7287,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="2" t="n">
+      <c r="A261" s="1" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -7332,7 +7318,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="2" t="n">
+      <c r="A262" s="1" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -7365,7 +7351,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="2" t="n">
+      <c r="A263" s="1" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -7396,7 +7382,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="2" t="n">
+      <c r="A264" s="1" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -7427,7 +7413,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="2" t="n">
+      <c r="A265" s="1" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -7460,7 +7446,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="2" t="n">
+      <c r="A266" s="1" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -7491,7 +7477,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="2" t="n">
+      <c r="A267" s="1" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -7522,7 +7508,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="2" t="n">
+      <c r="A268" s="1" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -7555,7 +7541,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="2" t="n">
+      <c r="A269" s="1" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -7586,7 +7572,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="2" t="n">
+      <c r="A270" s="1" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -7617,7 +7603,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="2" t="n">
+      <c r="A271" s="1" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -7650,7 +7636,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="2" t="n">
+      <c r="A272" s="1" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -7681,7 +7667,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="2" t="n">
+      <c r="A273" s="1" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7712,7 +7698,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="2" t="n">
+      <c r="A274" s="1" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7745,7 +7731,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="2" t="n">
+      <c r="A275" s="1" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7776,7 +7762,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="2" t="n">
+      <c r="A276" s="1" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7807,7 +7793,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="2" t="n">
+      <c r="A277" s="1" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7840,7 +7826,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="2" t="n">
+      <c r="A278" s="1" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7871,7 +7857,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="2" t="n">
+      <c r="A279" s="1" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7902,7 +7888,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="2" t="n">
+      <c r="A280" s="1" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7935,7 +7921,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="2" t="n">
+      <c r="A281" s="1" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7966,7 +7952,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="2" t="n">
+      <c r="A282" s="1" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7997,7 +7983,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="2" t="n">
+      <c r="A283" s="1" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -8030,7 +8016,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="2" t="n">
+      <c r="A284" s="1" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -8061,7 +8047,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="2" t="n">
+      <c r="A285" s="1" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -8092,7 +8078,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="2" t="n">
+      <c r="A286" s="1" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -8125,7 +8111,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="2" t="n">
+      <c r="A287" s="1" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -8156,7 +8142,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="2" t="n">
+      <c r="A288" s="1" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -8187,7 +8173,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="2" t="n">
+      <c r="A289" s="1" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -8220,7 +8206,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="2" t="n">
+      <c r="A290" s="1" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -8251,7 +8237,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="2" t="n">
+      <c r="A291" s="1" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -8282,7 +8268,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="2" t="n">
+      <c r="A292" s="1" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -8315,7 +8301,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="2" t="n">
+      <c r="A293" s="1" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -8346,7 +8332,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="2" t="n">
+      <c r="A294" s="1" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -8377,7 +8363,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="2" t="n">
+      <c r="A295" s="1" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -8410,7 +8396,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="2" t="n">
+      <c r="A296" s="1" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -8441,7 +8427,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="2" t="n">
+      <c r="A297" s="1" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -8472,7 +8458,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="2" t="n">
+      <c r="A298" s="1" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -8505,7 +8491,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="2" t="n">
+      <c r="A299" s="1" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -8536,7 +8522,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="2" t="n">
+      <c r="A300" s="1" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -8567,7 +8553,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="2" t="n">
+      <c r="A301" s="1" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -8600,7 +8586,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="2" t="n">
+      <c r="A302" s="1" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -8631,7 +8617,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="2" t="n">
+      <c r="A303" s="1" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -8662,7 +8648,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="2" t="n">
+      <c r="A304" s="1" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -8695,7 +8681,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="2" t="n">
+      <c r="A305" s="1" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8726,7 +8712,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="2" t="n">
+      <c r="A306" s="1" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8757,7 +8743,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="2" t="n">
+      <c r="A307" s="1" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8790,7 +8776,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="2" t="n">
+      <c r="A308" s="1" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8821,7 +8807,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="2" t="n">
+      <c r="A309" s="1" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8852,7 +8838,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="2" t="n">
+      <c r="A310" s="1" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8885,7 +8871,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="2" t="n">
+      <c r="A311" s="1" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8916,7 +8902,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="2" t="n">
+      <c r="A312" s="1" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8947,7 +8933,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="2" t="n">
+      <c r="A313" s="1" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8980,7 +8966,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="2" t="n">
+      <c r="A314" s="1" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -9011,7 +8997,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="2" t="n">
+      <c r="A315" s="1" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -9042,7 +9028,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="2" t="n">
+      <c r="A316" s="1" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -9075,7 +9061,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="2" t="n">
+      <c r="A317" s="1" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -9106,7 +9092,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="2" t="n">
+      <c r="A318" s="1" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -9137,7 +9123,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="2" t="n">
+      <c r="A319" s="1" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -9170,7 +9156,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="2" t="n">
+      <c r="A320" s="1" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -9201,7 +9187,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="2" t="n">
+      <c r="A321" s="1" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -9232,7 +9218,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="2" t="n">
+      <c r="A322" s="1" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -9265,7 +9251,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="2" t="n">
+      <c r="A323" s="1" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -9296,7 +9282,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="2" t="n">
+      <c r="A324" s="1" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -9327,7 +9313,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="2" t="n">
+      <c r="A325" s="1" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -9360,7 +9346,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="2" t="n">
+      <c r="A326" s="1" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -9391,7 +9377,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="2" t="n">
+      <c r="A327" s="1" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -9422,7 +9408,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="2" t="n">
+      <c r="A328" s="1" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -9455,7 +9441,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="2" t="n">
+      <c r="A329" s="1" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -9486,7 +9472,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="2" t="n">
+      <c r="A330" s="1" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -9517,7 +9503,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="2" t="n">
+      <c r="A331" s="1" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -9550,7 +9536,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="2" t="n">
+      <c r="A332" s="1" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -9581,7 +9567,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="2" t="n">
+      <c r="A333" s="1" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -9612,7 +9598,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="2" t="n">
+      <c r="A334" s="1" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -9645,7 +9631,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="2" t="n">
+      <c r="A335" s="1" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -9676,7 +9662,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="2" t="n">
+      <c r="A336" s="1" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9707,7 +9693,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="2" t="n">
+      <c r="A337" s="1" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9740,7 +9726,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="2" t="n">
+      <c r="A338" s="1" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9771,7 +9757,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="2" t="n">
+      <c r="A339" s="1" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9802,7 +9788,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="2" t="n">
+      <c r="A340" s="1" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9835,7 +9821,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="2" t="n">
+      <c r="A341" s="1" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9866,7 +9852,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="2" t="n">
+      <c r="A342" s="1" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9897,7 +9883,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="2" t="n">
+      <c r="A343" s="1" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9930,7 +9916,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="2" t="n">
+      <c r="A344" s="1" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9961,7 +9947,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="2" t="n">
+      <c r="A345" s="1" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9992,7 +9978,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="2" t="n">
+      <c r="A346" s="1" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -10025,7 +10011,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="2" t="n">
+      <c r="A347" s="1" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -10056,7 +10042,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="2" t="n">
+      <c r="A348" s="1" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -10087,7 +10073,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="2" t="n">
+      <c r="A349" s="1" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -10120,7 +10106,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="2" t="n">
+      <c r="A350" s="1" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -10151,7 +10137,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="2" t="n">
+      <c r="A351" s="1" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -10182,7 +10168,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="2" t="n">
+      <c r="A352" s="1" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -10215,7 +10201,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="2" t="n">
+      <c r="A353" s="1" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -10246,7 +10232,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="2" t="n">
+      <c r="A354" s="1" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -10277,7 +10263,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="2" t="n">
+      <c r="A355" s="1" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -10310,7 +10296,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="2" t="n">
+      <c r="A356" s="1" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -10341,7 +10327,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="2" t="n">
+      <c r="A357" s="1" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -10372,7 +10358,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="2" t="n">
+      <c r="A358" s="1" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -10405,7 +10391,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="2" t="n">
+      <c r="A359" s="1" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -10436,7 +10422,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="2" t="n">
+      <c r="A360" s="1" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -10467,7 +10453,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="2" t="n">
+      <c r="A361" s="1" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -10500,7 +10486,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="2" t="n">
+      <c r="A362" s="1" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -10531,7 +10517,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="2" t="n">
+      <c r="A363" s="1" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -10562,7 +10548,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="2" t="n">
+      <c r="A364" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -10595,7 +10581,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="2" t="n">
+      <c r="A365" s="1" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -10626,7 +10612,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="2" t="n">
+      <c r="A366" s="1" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -10657,7 +10643,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="2" t="n">
+      <c r="A367" s="1" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -10690,7 +10676,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="2" t="n">
+      <c r="A368" s="1" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10721,7 +10707,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="2" t="n">
+      <c r="A369" s="1" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10752,7 +10738,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="2" t="n">
+      <c r="A370" s="1" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10785,7 +10771,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="2" t="n">
+      <c r="A371" s="1" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10816,7 +10802,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="2" t="n">
+      <c r="A372" s="1" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10847,7 +10833,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="2" t="n">
+      <c r="A373" s="1" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10880,7 +10866,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="2" t="n">
+      <c r="A374" s="1" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10911,7 +10897,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="2" t="n">
+      <c r="A375" s="1" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10942,7 +10928,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="2" t="n">
+      <c r="A376" s="1" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10975,7 +10961,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="2" t="n">
+      <c r="A377" s="1" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -11006,7 +10992,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="2" t="n">
+      <c r="A378" s="1" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -11037,7 +11023,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="2" t="n">
+      <c r="A379" s="1" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -11070,7 +11056,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="2" t="n">
+      <c r="A380" s="1" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -11101,7 +11087,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="2" t="n">
+      <c r="A381" s="1" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -11132,7 +11118,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="2" t="n">
+      <c r="A382" s="1" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -11165,7 +11151,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="2" t="n">
+      <c r="A383" s="1" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -11196,7 +11182,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="2" t="n">
+      <c r="A384" s="1" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -11227,7 +11213,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="2" t="n">
+      <c r="A385" s="1" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -11260,7 +11246,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="2" t="n">
+      <c r="A386" s="1" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -11291,7 +11277,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="2" t="n">
+      <c r="A387" s="1" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -11322,7 +11308,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="2" t="n">
+      <c r="A388" s="1" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -11355,7 +11341,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="2" t="n">
+      <c r="A389" s="1" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -11386,7 +11372,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="2" t="n">
+      <c r="A390" s="1" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -11417,7 +11403,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="2" t="n">
+      <c r="A391" s="1" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -11450,7 +11436,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="2" t="n">
+      <c r="A392" s="1" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -11481,7 +11467,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="2" t="n">
+      <c r="A393" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -11512,7 +11498,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="2" t="n">
+      <c r="A394" s="1" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -11545,7 +11531,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="2" t="n">
+      <c r="A395" s="1" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -11576,7 +11562,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="2" t="n">
+      <c r="A396" s="1" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -11607,7 +11593,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="2" t="n">
+      <c r="A397" s="1" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -11640,7 +11626,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="2" t="n">
+      <c r="A398" s="1" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -11671,7 +11657,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="2" t="n">
+      <c r="A399" s="1" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11702,7 +11688,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="2" t="n">
+      <c r="A400" s="1" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11735,7 +11721,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="2" t="n">
+      <c r="A401" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11766,7 +11752,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="2" t="n">
+      <c r="A402" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11797,7 +11783,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="2" t="n">
+      <c r="A403" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11830,7 +11816,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="2" t="n">
+      <c r="A404" s="1" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11861,7 +11847,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="2" t="n">
+      <c r="A405" s="1" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11892,7 +11878,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="2" t="n">
+      <c r="A406" s="1" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11925,7 +11911,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="2" t="n">
+      <c r="A407" s="1" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11956,7 +11942,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="2" t="n">
+      <c r="A408" s="1" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11987,7 +11973,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="2" t="n">
+      <c r="A409" s="1" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -12020,7 +12006,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="2" t="n">
+      <c r="A410" s="1" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -12051,7 +12037,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="2" t="n">
+      <c r="A411" s="1" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -12082,7 +12068,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="2" t="n">
+      <c r="A412" s="1" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -12115,7 +12101,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="2" t="n">
+      <c r="A413" s="1" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -12146,7 +12132,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="2" t="n">
+      <c r="A414" s="1" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -12177,7 +12163,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="2" t="n">
+      <c r="A415" s="1" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -12210,7 +12196,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="2" t="n">
+      <c r="A416" s="1" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -12241,7 +12227,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="2" t="n">
+      <c r="A417" s="1" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -12272,7 +12258,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="2" t="n">
+      <c r="A418" s="1" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -12305,7 +12291,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="2" t="n">
+      <c r="A419" s="1" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -12336,7 +12322,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="2" t="n">
+      <c r="A420" s="1" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -12367,7 +12353,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="2" t="n">
+      <c r="A421" s="1" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -12400,7 +12386,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="2" t="n">
+      <c r="A422" s="1" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -12431,7 +12417,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="2" t="n">
+      <c r="A423" s="1" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -12462,7 +12448,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="2" t="n">
+      <c r="A424" s="1" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -12495,7 +12481,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="2" t="n">
+      <c r="A425" s="1" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -12526,7 +12512,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="2" t="n">
+      <c r="A426" s="1" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -12557,7 +12543,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="2" t="n">
+      <c r="A427" s="1" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -12590,7 +12576,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="2" t="n">
+      <c r="A428" s="1" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -12621,7 +12607,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="2" t="n">
+      <c r="A429" s="1" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -12652,7 +12638,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="2" t="n">
+      <c r="A430" s="1" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -12685,7 +12671,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="2" t="n">
+      <c r="A431" s="1" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12716,7 +12702,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="2" t="n">
+      <c r="A432" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12747,7 +12733,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="2" t="n">
+      <c r="A433" s="1" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12780,7 +12766,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="2" t="n">
+      <c r="A434" s="1" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12811,7 +12797,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="2" t="n">
+      <c r="A435" s="1" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12842,7 +12828,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="2" t="n">
+      <c r="A436" s="1" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12875,7 +12861,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="2" t="n">
+      <c r="A437" s="1" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12906,7 +12892,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="2" t="n">
+      <c r="A438" s="1" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12937,7 +12923,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="2" t="n">
+      <c r="A439" s="1" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12970,7 +12956,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="2" t="n">
+      <c r="A440" s="1" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -13001,7 +12987,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="2" t="n">
+      <c r="A441" s="1" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -13032,7 +13018,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="2" t="n">
+      <c r="A442" s="1" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -13065,7 +13051,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="2" t="n">
+      <c r="A443" s="1" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -13096,7 +13082,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="2" t="n">
+      <c r="A444" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -13127,7 +13113,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="2" t="n">
+      <c r="A445" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -13160,7 +13146,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="2" t="n">
+      <c r="A446" s="1" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -13191,7 +13177,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="2" t="n">
+      <c r="A447" s="1" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -13222,7 +13208,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="2" t="n">
+      <c r="A448" s="1" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -13255,7 +13241,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="2" t="n">
+      <c r="A449" s="1" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -13286,7 +13272,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="2" t="n">
+      <c r="A450" s="1" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -13317,7 +13303,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="2" t="n">
+      <c r="A451" s="1" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -13350,7 +13336,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="2" t="n">
+      <c r="A452" s="1" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -13381,7 +13367,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="2" t="n">
+      <c r="A453" s="1" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -13412,7 +13398,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="2" t="n">
+      <c r="A454" s="1" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -13445,7 +13431,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="2" t="n">
+      <c r="A455" s="1" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -13476,7 +13462,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="2" t="n">
+      <c r="A456" s="1" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -13507,7 +13493,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="2" t="n">
+      <c r="A457" s="1" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -13540,7 +13526,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="2" t="n">
+      <c r="A458" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -13571,7 +13557,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="2" t="n">
+      <c r="A459" s="1" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -13602,7 +13588,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="2" t="n">
+      <c r="A460" s="1" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -13635,7 +13621,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="2" t="n">
+      <c r="A461" s="1" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -13666,7 +13652,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="2" t="n">
+      <c r="A462" s="1" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -13697,7 +13683,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="2" t="n">
+      <c r="A463" s="1" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13730,7 +13716,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="2" t="n">
+      <c r="A464" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13761,7 +13747,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="2" t="n">
+      <c r="A465" s="1" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13792,7 +13778,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="2" t="n">
+      <c r="A466" s="1" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13825,7 +13811,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="2" t="n">
+      <c r="A467" s="1" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13856,7 +13842,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="2" t="n">
+      <c r="A468" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13887,7 +13873,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="2" t="n">
+      <c r="A469" s="1" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13920,7 +13906,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="2" t="n">
+      <c r="A470" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13951,7 +13937,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="2" t="n">
+      <c r="A471" s="1" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13982,7 +13968,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="2" t="n">
+      <c r="A472" s="1" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -14015,7 +14001,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="2" t="n">
+      <c r="A473" s="1" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -14046,7 +14032,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="2" t="n">
+      <c r="A474" s="1" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -14077,7 +14063,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="2" t="n">
+      <c r="A475" s="1" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -14110,7 +14096,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="2" t="n">
+      <c r="A476" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -14141,7 +14127,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="2" t="n">
+      <c r="A477" s="1" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -14172,7 +14158,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="2" t="n">
+      <c r="A478" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -14205,7 +14191,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="2" t="n">
+      <c r="A479" s="1" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -14236,7 +14222,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="2" t="n">
+      <c r="A480" s="1" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -14267,7 +14253,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="2" t="n">
+      <c r="A481" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -14300,7 +14286,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="2" t="n">
+      <c r="A482" s="1" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -14331,7 +14317,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="2" t="n">
+      <c r="A483" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -14362,7 +14348,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="2" t="n">
+      <c r="A484" s="1" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -14395,7 +14381,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="2" t="n">
+      <c r="A485" s="1" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -14426,7 +14412,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="2" t="n">
+      <c r="A486" s="1" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -14457,7 +14443,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="2" t="n">
+      <c r="A487" s="1" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -14490,7 +14476,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="2" t="n">
+      <c r="A488" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -14521,7 +14507,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="2" t="n">
+      <c r="A489" s="1" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -14552,7 +14538,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="2" t="n">
+      <c r="A490" s="1" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -14585,7 +14571,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="2" t="n">
+      <c r="A491" s="1" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -14616,7 +14602,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="2" t="n">
+      <c r="A492" s="1" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -14647,7 +14633,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="2" t="n">
+      <c r="A493" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -14680,7 +14666,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="2" t="n">
+      <c r="A494" s="1" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14711,7 +14697,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="2" t="n">
+      <c r="A495" s="1" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14742,7 +14728,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="2" t="n">
+      <c r="A496" s="1" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14775,7 +14761,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="2" t="n">
+      <c r="A497" s="1" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14806,7 +14792,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="2" t="n">
+      <c r="A498" s="1" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14837,7 +14823,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="2" t="n">
+      <c r="A499" s="1" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14870,7 +14856,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="2" t="n">
+      <c r="A500" s="1" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14901,7 +14887,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="2" t="n">
+      <c r="A501" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14932,7 +14918,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="2" t="n">
+      <c r="A502" s="1" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>
@@ -14947,7 +14933,7 @@
       <c r="G502" t="inlineStr"/>
       <c r="H502" t="inlineStr"/>
       <c r="I502" t="n">
-        <v>4.638508245598602</v>
+        <v>4.639088404191552</v>
       </c>
       <c r="J502" t="n">
         <v>4.596689494135473</v>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +48,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,64 +435,64 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>GDPyoy</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>EURIBOR 3M</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>EcSent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IPall</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>CONSindex</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>retail</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unemployment</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>HICP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Brent</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>STOXX</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>31078</v>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -497,7 +511,7 @@
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>31106</v>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -516,7 +530,7 @@
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>31137</v>
       </c>
       <c r="B4" t="n">
@@ -537,7 +551,7 @@
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>31167</v>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -556,7 +570,7 @@
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>31198</v>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -575,7 +589,7 @@
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>31228</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +610,7 @@
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>31259</v>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -615,7 +629,7 @@
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>31290</v>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -634,7 +648,7 @@
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>31320</v>
       </c>
       <c r="B10" t="n">
@@ -655,7 +669,7 @@
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>31351</v>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -674,7 +688,7 @@
       <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>31381</v>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -693,7 +707,7 @@
       <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>31412</v>
       </c>
       <c r="B13" t="n">
@@ -714,7 +728,7 @@
       <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>31443</v>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -733,7 +747,7 @@
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>31471</v>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -752,7 +766,7 @@
       <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>31502</v>
       </c>
       <c r="B16" t="n">
@@ -773,7 +787,7 @@
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>31532</v>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -792,7 +806,7 @@
       <c r="K17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>31563</v>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -811,7 +825,7 @@
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>31593</v>
       </c>
       <c r="B19" t="n">
@@ -832,7 +846,7 @@
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>31624</v>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -851,7 +865,7 @@
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>31655</v>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -870,7 +884,7 @@
       <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>31685</v>
       </c>
       <c r="B22" t="n">
@@ -891,7 +905,7 @@
       <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>31716</v>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -910,7 +924,7 @@
       <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>31746</v>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -929,7 +943,7 @@
       <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>31777</v>
       </c>
       <c r="B25" t="n">
@@ -950,7 +964,7 @@
       <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>31808</v>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -969,7 +983,7 @@
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>31836</v>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -988,7 +1002,7 @@
       <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>31867</v>
       </c>
       <c r="B28" t="n">
@@ -1009,7 +1023,7 @@
       <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>31897</v>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1028,7 +1042,7 @@
       <c r="K29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>31928</v>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1047,7 +1061,7 @@
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>31958</v>
       </c>
       <c r="B31" t="n">
@@ -1068,7 +1082,7 @@
       <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>31989</v>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1087,7 +1101,7 @@
       <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>32020</v>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1106,7 +1120,7 @@
       <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>32050</v>
       </c>
       <c r="B34" t="n">
@@ -1127,7 +1141,7 @@
       <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>32081</v>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1146,7 +1160,7 @@
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>32111</v>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1165,7 +1179,7 @@
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>32142</v>
       </c>
       <c r="B37" t="n">
@@ -1186,7 +1200,7 @@
       <c r="K37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>32173</v>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1205,7 +1219,7 @@
       <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>32202</v>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1224,7 +1238,7 @@
       <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>32233</v>
       </c>
       <c r="B40" t="n">
@@ -1245,7 +1259,7 @@
       <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>32263</v>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1264,7 +1278,7 @@
       <c r="K41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>32294</v>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1283,7 +1297,7 @@
       <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>32324</v>
       </c>
       <c r="B43" t="n">
@@ -1304,7 +1318,7 @@
       <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>32355</v>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1323,7 +1337,7 @@
       <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>32386</v>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1342,7 +1356,7 @@
       <c r="K45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>32416</v>
       </c>
       <c r="B46" t="n">
@@ -1363,7 +1377,7 @@
       <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>32447</v>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1382,7 +1396,7 @@
       <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>32477</v>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1401,7 +1415,7 @@
       <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>32508</v>
       </c>
       <c r="B49" t="n">
@@ -1422,7 +1436,7 @@
       <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>32539</v>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1441,7 +1455,7 @@
       <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>32567</v>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1460,7 +1474,7 @@
       <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>32598</v>
       </c>
       <c r="B52" t="n">
@@ -1481,7 +1495,7 @@
       <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>32628</v>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1500,7 +1514,7 @@
       <c r="K53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>32659</v>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1519,7 +1533,7 @@
       <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>32689</v>
       </c>
       <c r="B55" t="n">
@@ -1540,7 +1554,7 @@
       <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>32720</v>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1559,7 +1573,7 @@
       <c r="K56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>32751</v>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1578,7 +1592,7 @@
       <c r="K57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>32781</v>
       </c>
       <c r="B58" t="n">
@@ -1599,7 +1613,7 @@
       <c r="K58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>32812</v>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -1618,7 +1632,7 @@
       <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>32842</v>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -1637,7 +1651,7 @@
       <c r="K60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>32873</v>
       </c>
       <c r="B61" t="n">
@@ -1658,7 +1672,7 @@
       <c r="K61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>32904</v>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -1681,7 +1695,7 @@
       <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>32932</v>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -1704,7 +1718,7 @@
       <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>32963</v>
       </c>
       <c r="B64" t="n">
@@ -1729,7 +1743,7 @@
       <c r="K64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>32993</v>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -1752,7 +1766,7 @@
       <c r="K65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>33024</v>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -1775,7 +1789,7 @@
       <c r="K66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>33054</v>
       </c>
       <c r="B67" t="n">
@@ -1800,7 +1814,7 @@
       <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>33085</v>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -1823,7 +1837,7 @@
       <c r="K68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>33116</v>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -1846,7 +1860,7 @@
       <c r="K69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>33146</v>
       </c>
       <c r="B70" t="n">
@@ -1871,7 +1885,7 @@
       <c r="K70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>33177</v>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1894,7 +1908,7 @@
       <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>33207</v>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1917,7 +1931,7 @@
       <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>33238</v>
       </c>
       <c r="B73" t="n">
@@ -1942,7 +1956,7 @@
       <c r="K73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>33269</v>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1965,7 +1979,7 @@
       <c r="K74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>33297</v>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1988,7 +2002,7 @@
       <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>33328</v>
       </c>
       <c r="B76" t="n">
@@ -2013,7 +2027,7 @@
       <c r="K76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>33358</v>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2036,7 +2050,7 @@
       <c r="K77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>33389</v>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -2059,7 +2073,7 @@
       <c r="K78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>33419</v>
       </c>
       <c r="B79" t="n">
@@ -2084,7 +2098,7 @@
       <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>33450</v>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2107,7 +2121,7 @@
       <c r="K80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>33481</v>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -2130,7 +2144,7 @@
       <c r="K81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>33511</v>
       </c>
       <c r="B82" t="n">
@@ -2155,7 +2169,7 @@
       <c r="K82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>33542</v>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -2178,7 +2192,7 @@
       <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>33572</v>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2201,7 +2215,7 @@
       <c r="K84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>33603</v>
       </c>
       <c r="B85" t="n">
@@ -2226,7 +2240,7 @@
       <c r="K85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>33634</v>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -2249,7 +2263,7 @@
       <c r="K86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>33663</v>
       </c>
       <c r="B87" t="inlineStr"/>
@@ -2272,7 +2286,7 @@
       <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>33694</v>
       </c>
       <c r="B88" t="n">
@@ -2297,7 +2311,7 @@
       <c r="K88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>33724</v>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -2320,7 +2334,7 @@
       <c r="K89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>33755</v>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -2343,7 +2357,7 @@
       <c r="K90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>33785</v>
       </c>
       <c r="B91" t="n">
@@ -2368,7 +2382,7 @@
       <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>33816</v>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -2391,7 +2405,7 @@
       <c r="K92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>33847</v>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -2414,7 +2428,7 @@
       <c r="K93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>33877</v>
       </c>
       <c r="B94" t="n">
@@ -2439,7 +2453,7 @@
       <c r="K94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>33908</v>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -2462,7 +2476,7 @@
       <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>33938</v>
       </c>
       <c r="B96" t="inlineStr"/>
@@ -2485,7 +2499,7 @@
       <c r="K96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>33969</v>
       </c>
       <c r="B97" t="n">
@@ -2510,7 +2524,7 @@
       <c r="K97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>34000</v>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -2533,7 +2547,7 @@
       <c r="K98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>34028</v>
       </c>
       <c r="B99" t="inlineStr"/>
@@ -2556,7 +2570,7 @@
       <c r="K99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>34059</v>
       </c>
       <c r="B100" t="n">
@@ -2581,7 +2595,7 @@
       <c r="K100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>34089</v>
       </c>
       <c r="B101" t="inlineStr"/>
@@ -2604,7 +2618,7 @@
       <c r="K101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>34120</v>
       </c>
       <c r="B102" t="inlineStr"/>
@@ -2627,7 +2641,7 @@
       <c r="K102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>34150</v>
       </c>
       <c r="B103" t="n">
@@ -2652,7 +2666,7 @@
       <c r="K103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>34181</v>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -2675,7 +2689,7 @@
       <c r="K104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>34212</v>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -2698,7 +2712,7 @@
       <c r="K105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>34242</v>
       </c>
       <c r="B106" t="n">
@@ -2723,7 +2737,7 @@
       <c r="K106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>34273</v>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -2746,7 +2760,7 @@
       <c r="K107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>34303</v>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -2769,7 +2783,7 @@
       <c r="K108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>34334</v>
       </c>
       <c r="B109" t="n">
@@ -2794,7 +2808,7 @@
       <c r="K109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>34365</v>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -2819,7 +2833,7 @@
       <c r="K110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>34393</v>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -2844,7 +2858,7 @@
       <c r="K111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>34424</v>
       </c>
       <c r="B112" t="n">
@@ -2871,7 +2885,7 @@
       <c r="K112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>34454</v>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -2896,7 +2910,7 @@
       <c r="K113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>34485</v>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -2921,7 +2935,7 @@
       <c r="K114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>34515</v>
       </c>
       <c r="B115" t="n">
@@ -2948,7 +2962,7 @@
       <c r="K115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>34546</v>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -2973,7 +2987,7 @@
       <c r="K116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>34577</v>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -2998,7 +3012,7 @@
       <c r="K117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>34607</v>
       </c>
       <c r="B118" t="n">
@@ -3025,7 +3039,7 @@
       <c r="K118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>34638</v>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -3050,7 +3064,7 @@
       <c r="K119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>34668</v>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -3075,7 +3089,7 @@
       <c r="K120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>34699</v>
       </c>
       <c r="B121" t="n">
@@ -3102,7 +3116,7 @@
       <c r="K121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>34730</v>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -3127,7 +3141,7 @@
       <c r="K122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>34758</v>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -3152,7 +3166,7 @@
       <c r="K123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>34789</v>
       </c>
       <c r="B124" t="n">
@@ -3179,7 +3193,7 @@
       <c r="K124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>34819</v>
       </c>
       <c r="B125" t="inlineStr"/>
@@ -3204,7 +3218,7 @@
       <c r="K125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>34850</v>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -3229,7 +3243,7 @@
       <c r="K126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>34880</v>
       </c>
       <c r="B127" t="n">
@@ -3256,7 +3270,7 @@
       <c r="K127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>34911</v>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -3281,7 +3295,7 @@
       <c r="K128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>34942</v>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -3306,7 +3320,7 @@
       <c r="K129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>34972</v>
       </c>
       <c r="B130" t="n">
@@ -3333,7 +3347,7 @@
       <c r="K130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>35003</v>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -3358,7 +3372,7 @@
       <c r="K131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>35033</v>
       </c>
       <c r="B132" t="inlineStr"/>
@@ -3383,7 +3397,7 @@
       <c r="K132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>35064</v>
       </c>
       <c r="B133" t="n">
@@ -3410,7 +3424,7 @@
       <c r="K133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>35095</v>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -3437,7 +3451,7 @@
       <c r="K134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>35124</v>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -3464,7 +3478,7 @@
       <c r="K135" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>35155</v>
       </c>
       <c r="B136" t="n">
@@ -3493,7 +3507,7 @@
       <c r="K136" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>35185</v>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -3520,7 +3534,7 @@
       <c r="K137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>35216</v>
       </c>
       <c r="B138" t="inlineStr"/>
@@ -3547,7 +3561,7 @@
       <c r="K138" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>35246</v>
       </c>
       <c r="B139" t="n">
@@ -3576,7 +3590,7 @@
       <c r="K139" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>35277</v>
       </c>
       <c r="B140" t="inlineStr"/>
@@ -3603,7 +3617,7 @@
       <c r="K140" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>35308</v>
       </c>
       <c r="B141" t="inlineStr"/>
@@ -3630,7 +3644,7 @@
       <c r="K141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>35338</v>
       </c>
       <c r="B142" t="n">
@@ -3659,7 +3673,7 @@
       <c r="K142" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>35369</v>
       </c>
       <c r="B143" t="inlineStr"/>
@@ -3686,7 +3700,7 @@
       <c r="K143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>35399</v>
       </c>
       <c r="B144" t="inlineStr"/>
@@ -3713,7 +3727,7 @@
       <c r="K144" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>35430</v>
       </c>
       <c r="B145" t="n">
@@ -3742,7 +3756,7 @@
       <c r="K145" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>35461</v>
       </c>
       <c r="B146" t="inlineStr"/>
@@ -3769,7 +3783,7 @@
       <c r="K146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>35489</v>
       </c>
       <c r="B147" t="inlineStr"/>
@@ -3796,7 +3810,7 @@
       <c r="K147" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>35520</v>
       </c>
       <c r="B148" t="n">
@@ -3825,7 +3839,7 @@
       <c r="K148" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>35550</v>
       </c>
       <c r="B149" t="inlineStr"/>
@@ -3852,7 +3866,7 @@
       <c r="K149" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>35581</v>
       </c>
       <c r="B150" t="inlineStr"/>
@@ -3879,7 +3893,7 @@
       <c r="K150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>35611</v>
       </c>
       <c r="B151" t="n">
@@ -3908,7 +3922,7 @@
       <c r="K151" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>35642</v>
       </c>
       <c r="B152" t="inlineStr"/>
@@ -3935,7 +3949,7 @@
       <c r="K152" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>35673</v>
       </c>
       <c r="B153" t="inlineStr"/>
@@ -3962,7 +3976,7 @@
       <c r="K153" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>35703</v>
       </c>
       <c r="B154" t="n">
@@ -3991,7 +4005,7 @@
       <c r="K154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>35734</v>
       </c>
       <c r="B155" t="inlineStr"/>
@@ -4018,7 +4032,7 @@
       <c r="K155" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>35764</v>
       </c>
       <c r="B156" t="inlineStr"/>
@@ -4045,7 +4059,7 @@
       <c r="K156" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>35795</v>
       </c>
       <c r="B157" t="n">
@@ -4074,7 +4088,7 @@
       <c r="K157" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>35826</v>
       </c>
       <c r="B158" t="inlineStr"/>
@@ -4101,7 +4115,7 @@
       <c r="K158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>35854</v>
       </c>
       <c r="B159" t="inlineStr"/>
@@ -4128,7 +4142,7 @@
       <c r="K159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>35885</v>
       </c>
       <c r="B160" t="n">
@@ -4157,7 +4171,7 @@
       <c r="K160" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>35915</v>
       </c>
       <c r="B161" t="inlineStr"/>
@@ -4184,7 +4198,7 @@
       <c r="K161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>35946</v>
       </c>
       <c r="B162" t="inlineStr"/>
@@ -4211,7 +4225,7 @@
       <c r="K162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>35976</v>
       </c>
       <c r="B163" t="n">
@@ -4240,7 +4254,7 @@
       <c r="K163" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>36007</v>
       </c>
       <c r="B164" t="inlineStr"/>
@@ -4267,7 +4281,7 @@
       <c r="K164" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>36038</v>
       </c>
       <c r="B165" t="inlineStr"/>
@@ -4294,7 +4308,7 @@
       <c r="K165" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>36068</v>
       </c>
       <c r="B166" t="n">
@@ -4323,7 +4337,7 @@
       <c r="K166" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>36099</v>
       </c>
       <c r="B167" t="inlineStr"/>
@@ -4350,7 +4364,7 @@
       <c r="K167" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>36129</v>
       </c>
       <c r="B168" t="inlineStr"/>
@@ -4377,7 +4391,7 @@
       <c r="K168" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>36160</v>
       </c>
       <c r="B169" t="n">
@@ -4406,7 +4420,7 @@
       <c r="K169" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>36191</v>
       </c>
       <c r="B170" t="inlineStr"/>
@@ -4437,7 +4451,7 @@
       <c r="K170" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>36219</v>
       </c>
       <c r="B171" t="inlineStr"/>
@@ -4468,7 +4482,7 @@
       <c r="K171" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>36250</v>
       </c>
       <c r="B172" t="n">
@@ -4501,7 +4515,7 @@
       <c r="K172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>36280</v>
       </c>
       <c r="B173" t="inlineStr"/>
@@ -4532,7 +4546,7 @@
       <c r="K173" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>36311</v>
       </c>
       <c r="B174" t="inlineStr"/>
@@ -4563,7 +4577,7 @@
       <c r="K174" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>36341</v>
       </c>
       <c r="B175" t="n">
@@ -4596,7 +4610,7 @@
       <c r="K175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>36372</v>
       </c>
       <c r="B176" t="inlineStr"/>
@@ -4627,7 +4641,7 @@
       <c r="K176" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>36403</v>
       </c>
       <c r="B177" t="inlineStr"/>
@@ -4658,7 +4672,7 @@
       <c r="K177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>36433</v>
       </c>
       <c r="B178" t="n">
@@ -4691,7 +4705,7 @@
       <c r="K178" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>36464</v>
       </c>
       <c r="B179" t="inlineStr"/>
@@ -4722,7 +4736,7 @@
       <c r="K179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>36494</v>
       </c>
       <c r="B180" t="inlineStr"/>
@@ -4753,7 +4767,7 @@
       <c r="K180" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>36525</v>
       </c>
       <c r="B181" t="n">
@@ -4786,7 +4800,7 @@
       <c r="K181" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>36556</v>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -4817,7 +4831,7 @@
       <c r="K182" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>36585</v>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -4848,7 +4862,7 @@
       <c r="K183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>36616</v>
       </c>
       <c r="B184" t="n">
@@ -4881,7 +4895,7 @@
       <c r="K184" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>36646</v>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -4912,7 +4926,7 @@
       <c r="K185" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>36677</v>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -4943,7 +4957,7 @@
       <c r="K186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>36707</v>
       </c>
       <c r="B187" t="n">
@@ -4976,7 +4990,7 @@
       <c r="K187" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>36738</v>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -5007,7 +5021,7 @@
       <c r="K188" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>36769</v>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -5038,7 +5052,7 @@
       <c r="K189" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>36799</v>
       </c>
       <c r="B190" t="n">
@@ -5071,7 +5085,7 @@
       <c r="K190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>36830</v>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -5102,7 +5116,7 @@
       <c r="K191" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>36860</v>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -5133,7 +5147,7 @@
       <c r="K192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>36891</v>
       </c>
       <c r="B193" t="n">
@@ -5166,7 +5180,7 @@
       <c r="K193" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>36922</v>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -5197,7 +5211,7 @@
       <c r="K194" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>36950</v>
       </c>
       <c r="B195" t="inlineStr"/>
@@ -5228,7 +5242,7 @@
       <c r="K195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>36981</v>
       </c>
       <c r="B196" t="n">
@@ -5261,7 +5275,7 @@
       <c r="K196" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>37011</v>
       </c>
       <c r="B197" t="inlineStr"/>
@@ -5292,7 +5306,7 @@
       <c r="K197" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>37042</v>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -5323,7 +5337,7 @@
       <c r="K198" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>37072</v>
       </c>
       <c r="B199" t="n">
@@ -5356,7 +5370,7 @@
       <c r="K199" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>37103</v>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -5387,7 +5401,7 @@
       <c r="K200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>37134</v>
       </c>
       <c r="B201" t="inlineStr"/>
@@ -5418,7 +5432,7 @@
       <c r="K201" t="inlineStr"/>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>37164</v>
       </c>
       <c r="B202" t="n">
@@ -5451,7 +5465,7 @@
       <c r="K202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>37195</v>
       </c>
       <c r="B203" t="inlineStr"/>
@@ -5482,7 +5496,7 @@
       <c r="K203" t="inlineStr"/>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>37225</v>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -5513,7 +5527,7 @@
       <c r="K204" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>37256</v>
       </c>
       <c r="B205" t="n">
@@ -5546,7 +5560,7 @@
       <c r="K205" t="inlineStr"/>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>37287</v>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -5577,7 +5591,7 @@
       <c r="K206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>37315</v>
       </c>
       <c r="B207" t="inlineStr"/>
@@ -5608,7 +5622,7 @@
       <c r="K207" t="inlineStr"/>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>37346</v>
       </c>
       <c r="B208" t="n">
@@ -5641,7 +5655,7 @@
       <c r="K208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>37376</v>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -5672,7 +5686,7 @@
       <c r="K209" t="inlineStr"/>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>37407</v>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -5703,7 +5717,7 @@
       <c r="K210" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>37437</v>
       </c>
       <c r="B211" t="n">
@@ -5736,7 +5750,7 @@
       <c r="K211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>37468</v>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -5767,7 +5781,7 @@
       <c r="K212" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>37499</v>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -5798,7 +5812,7 @@
       <c r="K213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>37529</v>
       </c>
       <c r="B214" t="n">
@@ -5831,7 +5845,7 @@
       <c r="K214" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>37560</v>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -5862,7 +5876,7 @@
       <c r="K215" t="inlineStr"/>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>37590</v>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -5893,7 +5907,7 @@
       <c r="K216" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>37621</v>
       </c>
       <c r="B217" t="n">
@@ -5926,7 +5940,7 @@
       <c r="K217" t="inlineStr"/>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>37652</v>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -5957,7 +5971,7 @@
       <c r="K218" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>37680</v>
       </c>
       <c r="B219" t="inlineStr"/>
@@ -5988,7 +6002,7 @@
       <c r="K219" t="inlineStr"/>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>37711</v>
       </c>
       <c r="B220" t="n">
@@ -6021,7 +6035,7 @@
       <c r="K220" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>37741</v>
       </c>
       <c r="B221" t="inlineStr"/>
@@ -6052,7 +6066,7 @@
       <c r="K221" t="inlineStr"/>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>37772</v>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -6083,7 +6097,7 @@
       <c r="K222" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>37802</v>
       </c>
       <c r="B223" t="n">
@@ -6116,7 +6130,7 @@
       <c r="K223" t="inlineStr"/>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>37833</v>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -6147,7 +6161,7 @@
       <c r="K224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>37864</v>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -6178,7 +6192,7 @@
       <c r="K225" t="inlineStr"/>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>37894</v>
       </c>
       <c r="B226" t="n">
@@ -6211,7 +6225,7 @@
       <c r="K226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>37925</v>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -6242,7 +6256,7 @@
       <c r="K227" t="inlineStr"/>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>37955</v>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -6273,7 +6287,7 @@
       <c r="K228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>37986</v>
       </c>
       <c r="B229" t="n">
@@ -6306,7 +6320,7 @@
       <c r="K229" t="inlineStr"/>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>38017</v>
       </c>
       <c r="B230" t="inlineStr"/>
@@ -6337,7 +6351,7 @@
       <c r="K230" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>38046</v>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -6368,7 +6382,7 @@
       <c r="K231" t="inlineStr"/>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>38077</v>
       </c>
       <c r="B232" t="n">
@@ -6401,7 +6415,7 @@
       <c r="K232" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>38107</v>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -6432,7 +6446,7 @@
       <c r="K233" t="inlineStr"/>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>38138</v>
       </c>
       <c r="B234" t="inlineStr"/>
@@ -6463,7 +6477,7 @@
       <c r="K234" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>38168</v>
       </c>
       <c r="B235" t="n">
@@ -6496,7 +6510,7 @@
       <c r="K235" t="inlineStr"/>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>38199</v>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -6527,7 +6541,7 @@
       <c r="K236" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>38230</v>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -6558,7 +6572,7 @@
       <c r="K237" t="inlineStr"/>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>38260</v>
       </c>
       <c r="B238" t="n">
@@ -6591,7 +6605,7 @@
       <c r="K238" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>38291</v>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -6622,7 +6636,7 @@
       <c r="K239" t="inlineStr"/>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>38321</v>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -6653,7 +6667,7 @@
       <c r="K240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>38352</v>
       </c>
       <c r="B241" t="n">
@@ -6686,7 +6700,7 @@
       <c r="K241" t="inlineStr"/>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>38383</v>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -6717,7 +6731,7 @@
       <c r="K242" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>38411</v>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -6748,7 +6762,7 @@
       <c r="K243" t="inlineStr"/>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>38442</v>
       </c>
       <c r="B244" t="n">
@@ -6781,7 +6795,7 @@
       <c r="K244" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>38472</v>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -6812,7 +6826,7 @@
       <c r="K245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>38503</v>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -6843,7 +6857,7 @@
       <c r="K246" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>38533</v>
       </c>
       <c r="B247" t="n">
@@ -6876,7 +6890,7 @@
       <c r="K247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>38564</v>
       </c>
       <c r="B248" t="inlineStr"/>
@@ -6907,7 +6921,7 @@
       <c r="K248" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>38595</v>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -6938,7 +6952,7 @@
       <c r="K249" t="inlineStr"/>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>38625</v>
       </c>
       <c r="B250" t="n">
@@ -6971,7 +6985,7 @@
       <c r="K250" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" s="2" t="n">
         <v>38656</v>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -7002,7 +7016,7 @@
       <c r="K251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" s="2" t="n">
         <v>38686</v>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -7033,7 +7047,7 @@
       <c r="K252" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" s="2" t="n">
         <v>38717</v>
       </c>
       <c r="B253" t="n">
@@ -7066,7 +7080,7 @@
       <c r="K253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -7097,7 +7111,7 @@
       <c r="K254" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -7128,7 +7142,7 @@
       <c r="K255" t="inlineStr"/>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B256" t="n">
@@ -7161,7 +7175,7 @@
       <c r="K256" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -7192,7 +7206,7 @@
       <c r="K257" t="inlineStr"/>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -7223,7 +7237,7 @@
       <c r="K258" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B259" t="n">
@@ -7256,7 +7270,7 @@
       <c r="K259" t="inlineStr"/>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -7287,7 +7301,7 @@
       <c r="K260" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B261" t="inlineStr"/>
@@ -7318,7 +7332,7 @@
       <c r="K261" t="inlineStr"/>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B262" t="n">
@@ -7351,7 +7365,7 @@
       <c r="K262" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -7382,7 +7396,7 @@
       <c r="K263" t="inlineStr"/>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -7413,7 +7427,7 @@
       <c r="K264" t="inlineStr"/>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B265" t="n">
@@ -7446,7 +7460,7 @@
       <c r="K265" t="inlineStr"/>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B266" t="inlineStr"/>
@@ -7477,7 +7491,7 @@
       <c r="K266" t="inlineStr"/>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -7508,7 +7522,7 @@
       <c r="K267" t="inlineStr"/>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B268" t="n">
@@ -7541,7 +7555,7 @@
       <c r="K268" t="inlineStr"/>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B269" t="inlineStr"/>
@@ -7572,7 +7586,7 @@
       <c r="K269" t="inlineStr"/>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -7603,7 +7617,7 @@
       <c r="K270" t="inlineStr"/>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B271" t="n">
@@ -7636,7 +7650,7 @@
       <c r="K271" t="inlineStr"/>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -7667,7 +7681,7 @@
       <c r="K272" t="inlineStr"/>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -7698,7 +7712,7 @@
       <c r="K273" t="inlineStr"/>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B274" t="n">
@@ -7731,7 +7745,7 @@
       <c r="K274" t="inlineStr"/>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -7762,7 +7776,7 @@
       <c r="K275" t="inlineStr"/>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -7793,7 +7807,7 @@
       <c r="K276" t="inlineStr"/>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B277" t="n">
@@ -7826,7 +7840,7 @@
       <c r="K277" t="inlineStr"/>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -7857,7 +7871,7 @@
       <c r="K278" t="inlineStr"/>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -7888,7 +7902,7 @@
       <c r="K279" t="inlineStr"/>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B280" t="n">
@@ -7921,7 +7935,7 @@
       <c r="K280" t="inlineStr"/>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B281" t="inlineStr"/>
@@ -7952,7 +7966,7 @@
       <c r="K281" t="inlineStr"/>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -7983,7 +7997,7 @@
       <c r="K282" t="inlineStr"/>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B283" t="n">
@@ -8016,7 +8030,7 @@
       <c r="K283" t="inlineStr"/>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -8047,7 +8061,7 @@
       <c r="K284" t="inlineStr"/>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -8078,7 +8092,7 @@
       <c r="K285" t="inlineStr"/>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B286" t="n">
@@ -8111,7 +8125,7 @@
       <c r="K286" t="inlineStr"/>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -8142,7 +8156,7 @@
       <c r="K287" t="inlineStr"/>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B288" t="inlineStr"/>
@@ -8173,7 +8187,7 @@
       <c r="K288" t="inlineStr"/>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B289" t="n">
@@ -8206,7 +8220,7 @@
       <c r="K289" t="inlineStr"/>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -8237,7 +8251,7 @@
       <c r="K290" t="inlineStr"/>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -8268,7 +8282,7 @@
       <c r="K291" t="inlineStr"/>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B292" t="n">
@@ -8301,7 +8315,7 @@
       <c r="K292" t="inlineStr"/>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -8332,7 +8346,7 @@
       <c r="K293" t="inlineStr"/>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -8363,7 +8377,7 @@
       <c r="K294" t="inlineStr"/>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B295" t="n">
@@ -8396,7 +8410,7 @@
       <c r="K295" t="inlineStr"/>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -8427,7 +8441,7 @@
       <c r="K296" t="inlineStr"/>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -8458,7 +8472,7 @@
       <c r="K297" t="inlineStr"/>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B298" t="n">
@@ -8491,7 +8505,7 @@
       <c r="K298" t="inlineStr"/>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -8522,7 +8536,7 @@
       <c r="K299" t="inlineStr"/>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B300" t="inlineStr"/>
@@ -8553,7 +8567,7 @@
       <c r="K300" t="inlineStr"/>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B301" t="n">
@@ -8586,7 +8600,7 @@
       <c r="K301" t="inlineStr"/>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -8617,7 +8631,7 @@
       <c r="K302" t="inlineStr"/>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -8648,7 +8662,7 @@
       <c r="K303" t="inlineStr"/>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B304" t="n">
@@ -8681,7 +8695,7 @@
       <c r="K304" t="inlineStr"/>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -8712,7 +8726,7 @@
       <c r="K305" t="inlineStr"/>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -8743,7 +8757,7 @@
       <c r="K306" t="inlineStr"/>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B307" t="n">
@@ -8776,7 +8790,7 @@
       <c r="K307" t="inlineStr"/>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -8807,7 +8821,7 @@
       <c r="K308" t="inlineStr"/>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -8838,7 +8852,7 @@
       <c r="K309" t="inlineStr"/>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B310" t="n">
@@ -8871,7 +8885,7 @@
       <c r="K310" t="inlineStr"/>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -8902,7 +8916,7 @@
       <c r="K311" t="inlineStr"/>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -8933,7 +8947,7 @@
       <c r="K312" t="inlineStr"/>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B313" t="n">
@@ -8966,7 +8980,7 @@
       <c r="K313" t="inlineStr"/>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B314" t="inlineStr"/>
@@ -8997,7 +9011,7 @@
       <c r="K314" t="inlineStr"/>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -9028,7 +9042,7 @@
       <c r="K315" t="inlineStr"/>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B316" t="n">
@@ -9061,7 +9075,7 @@
       <c r="K316" t="inlineStr"/>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -9092,7 +9106,7 @@
       <c r="K317" t="inlineStr"/>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -9123,7 +9137,7 @@
       <c r="K318" t="inlineStr"/>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B319" t="n">
@@ -9156,7 +9170,7 @@
       <c r="K319" t="inlineStr"/>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -9187,7 +9201,7 @@
       <c r="K320" t="inlineStr"/>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -9218,7 +9232,7 @@
       <c r="K321" t="inlineStr"/>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B322" t="n">
@@ -9251,7 +9265,7 @@
       <c r="K322" t="inlineStr"/>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -9282,7 +9296,7 @@
       <c r="K323" t="inlineStr"/>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B324" t="inlineStr"/>
@@ -9313,7 +9327,7 @@
       <c r="K324" t="inlineStr"/>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B325" t="n">
@@ -9346,7 +9360,7 @@
       <c r="K325" t="inlineStr"/>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -9377,7 +9391,7 @@
       <c r="K326" t="inlineStr"/>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -9408,7 +9422,7 @@
       <c r="K327" t="inlineStr"/>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B328" t="n">
@@ -9441,7 +9455,7 @@
       <c r="K328" t="inlineStr"/>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -9472,7 +9486,7 @@
       <c r="K329" t="inlineStr"/>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -9503,7 +9517,7 @@
       <c r="K330" t="inlineStr"/>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B331" t="n">
@@ -9536,7 +9550,7 @@
       <c r="K331" t="inlineStr"/>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -9567,7 +9581,7 @@
       <c r="K332" t="inlineStr"/>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -9598,7 +9612,7 @@
       <c r="K333" t="inlineStr"/>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B334" t="n">
@@ -9631,7 +9645,7 @@
       <c r="K334" t="inlineStr"/>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -9662,7 +9676,7 @@
       <c r="K335" t="inlineStr"/>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -9693,7 +9707,7 @@
       <c r="K336" t="inlineStr"/>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B337" t="n">
@@ -9726,7 +9740,7 @@
       <c r="K337" t="inlineStr"/>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -9757,7 +9771,7 @@
       <c r="K338" t="inlineStr"/>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -9788,7 +9802,7 @@
       <c r="K339" t="inlineStr"/>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B340" t="n">
@@ -9821,7 +9835,7 @@
       <c r="K340" t="inlineStr"/>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B341" t="inlineStr"/>
@@ -9852,7 +9866,7 @@
       <c r="K341" t="inlineStr"/>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -9883,7 +9897,7 @@
       <c r="K342" t="inlineStr"/>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B343" t="n">
@@ -9916,7 +9930,7 @@
       <c r="K343" t="inlineStr"/>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -9947,7 +9961,7 @@
       <c r="K344" t="inlineStr"/>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -9978,7 +9992,7 @@
       <c r="K345" t="inlineStr"/>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B346" t="n">
@@ -10011,7 +10025,7 @@
       <c r="K346" t="inlineStr"/>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -10042,7 +10056,7 @@
       <c r="K347" t="inlineStr"/>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -10073,7 +10087,7 @@
       <c r="K348" t="inlineStr"/>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B349" t="n">
@@ -10106,7 +10120,7 @@
       <c r="K349" t="inlineStr"/>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -10137,7 +10151,7 @@
       <c r="K350" t="inlineStr"/>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -10168,7 +10182,7 @@
       <c r="K351" t="inlineStr"/>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B352" t="n">
@@ -10201,7 +10215,7 @@
       <c r="K352" t="inlineStr"/>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -10232,7 +10246,7 @@
       <c r="K353" t="inlineStr"/>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B354" t="inlineStr"/>
@@ -10263,7 +10277,7 @@
       <c r="K354" t="inlineStr"/>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B355" t="n">
@@ -10296,7 +10310,7 @@
       <c r="K355" t="inlineStr"/>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -10327,7 +10341,7 @@
       <c r="K356" t="inlineStr"/>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -10358,7 +10372,7 @@
       <c r="K357" t="inlineStr"/>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B358" t="n">
@@ -10391,7 +10405,7 @@
       <c r="K358" t="inlineStr"/>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B359" t="inlineStr"/>
@@ -10422,7 +10436,7 @@
       <c r="K359" t="inlineStr"/>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -10453,7 +10467,7 @@
       <c r="K360" t="inlineStr"/>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B361" t="n">
@@ -10486,7 +10500,7 @@
       <c r="K361" t="inlineStr"/>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -10517,7 +10531,7 @@
       <c r="K362" t="inlineStr"/>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -10548,7 +10562,7 @@
       <c r="K363" t="inlineStr"/>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B364" t="n">
@@ -10581,7 +10595,7 @@
       <c r="K364" t="inlineStr"/>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B365" t="inlineStr"/>
@@ -10612,7 +10626,7 @@
       <c r="K365" t="inlineStr"/>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -10643,7 +10657,7 @@
       <c r="K366" t="inlineStr"/>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B367" t="n">
@@ -10676,7 +10690,7 @@
       <c r="K367" t="inlineStr"/>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -10707,7 +10721,7 @@
       <c r="K368" t="inlineStr"/>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -10738,7 +10752,7 @@
       <c r="K369" t="inlineStr"/>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B370" t="n">
@@ -10771,7 +10785,7 @@
       <c r="K370" t="inlineStr"/>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -10802,7 +10816,7 @@
       <c r="K371" t="inlineStr"/>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B372" t="inlineStr"/>
@@ -10833,7 +10847,7 @@
       <c r="K372" t="inlineStr"/>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B373" t="n">
@@ -10866,7 +10880,7 @@
       <c r="K373" t="inlineStr"/>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -10897,7 +10911,7 @@
       <c r="K374" t="inlineStr"/>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -10928,7 +10942,7 @@
       <c r="K375" t="inlineStr"/>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B376" t="n">
@@ -10961,7 +10975,7 @@
       <c r="K376" t="inlineStr"/>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -10992,7 +11006,7 @@
       <c r="K377" t="inlineStr"/>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -11023,7 +11037,7 @@
       <c r="K378" t="inlineStr"/>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B379" t="n">
@@ -11056,7 +11070,7 @@
       <c r="K379" t="inlineStr"/>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -11087,7 +11101,7 @@
       <c r="K380" t="inlineStr"/>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -11118,7 +11132,7 @@
       <c r="K381" t="inlineStr"/>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B382" t="n">
@@ -11151,7 +11165,7 @@
       <c r="K382" t="inlineStr"/>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -11182,7 +11196,7 @@
       <c r="K383" t="inlineStr"/>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -11213,7 +11227,7 @@
       <c r="K384" t="inlineStr"/>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B385" t="n">
@@ -11246,7 +11260,7 @@
       <c r="K385" t="inlineStr"/>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -11277,7 +11291,7 @@
       <c r="K386" t="inlineStr"/>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -11308,7 +11322,7 @@
       <c r="K387" t="inlineStr"/>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B388" t="n">
@@ -11341,7 +11355,7 @@
       <c r="K388" t="inlineStr"/>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B389" t="inlineStr"/>
@@ -11372,7 +11386,7 @@
       <c r="K389" t="inlineStr"/>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B390" t="inlineStr"/>
@@ -11403,7 +11417,7 @@
       <c r="K390" t="inlineStr"/>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B391" t="n">
@@ -11436,7 +11450,7 @@
       <c r="K391" t="inlineStr"/>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B392" t="inlineStr"/>
@@ -11467,7 +11481,7 @@
       <c r="K392" t="inlineStr"/>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B393" t="inlineStr"/>
@@ -11498,7 +11512,7 @@
       <c r="K393" t="inlineStr"/>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B394" t="n">
@@ -11531,7 +11545,7 @@
       <c r="K394" t="inlineStr"/>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B395" t="inlineStr"/>
@@ -11562,7 +11576,7 @@
       <c r="K395" t="inlineStr"/>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B396" t="inlineStr"/>
@@ -11593,7 +11607,7 @@
       <c r="K396" t="inlineStr"/>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B397" t="n">
@@ -11626,7 +11640,7 @@
       <c r="K397" t="inlineStr"/>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B398" t="inlineStr"/>
@@ -11657,7 +11671,7 @@
       <c r="K398" t="inlineStr"/>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B399" t="inlineStr"/>
@@ -11688,7 +11702,7 @@
       <c r="K399" t="inlineStr"/>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B400" t="n">
@@ -11721,7 +11735,7 @@
       <c r="K400" t="inlineStr"/>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B401" t="inlineStr"/>
@@ -11752,7 +11766,7 @@
       <c r="K401" t="inlineStr"/>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B402" t="inlineStr"/>
@@ -11783,7 +11797,7 @@
       <c r="K402" t="inlineStr"/>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B403" t="n">
@@ -11816,7 +11830,7 @@
       <c r="K403" t="inlineStr"/>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B404" t="inlineStr"/>
@@ -11847,7 +11861,7 @@
       <c r="K404" t="inlineStr"/>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B405" t="inlineStr"/>
@@ -11878,7 +11892,7 @@
       <c r="K405" t="inlineStr"/>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B406" t="n">
@@ -11911,7 +11925,7 @@
       <c r="K406" t="inlineStr"/>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B407" t="inlineStr"/>
@@ -11942,7 +11956,7 @@
       <c r="K407" t="inlineStr"/>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B408" t="inlineStr"/>
@@ -11973,7 +11987,7 @@
       <c r="K408" t="inlineStr"/>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B409" t="n">
@@ -12006,7 +12020,7 @@
       <c r="K409" t="inlineStr"/>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B410" t="inlineStr"/>
@@ -12037,7 +12051,7 @@
       <c r="K410" t="inlineStr"/>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B411" t="inlineStr"/>
@@ -12068,7 +12082,7 @@
       <c r="K411" t="inlineStr"/>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B412" t="n">
@@ -12101,7 +12115,7 @@
       <c r="K412" t="inlineStr"/>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B413" t="inlineStr"/>
@@ -12132,7 +12146,7 @@
       <c r="K413" t="inlineStr"/>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B414" t="inlineStr"/>
@@ -12163,7 +12177,7 @@
       <c r="K414" t="inlineStr"/>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B415" t="n">
@@ -12196,7 +12210,7 @@
       <c r="K415" t="inlineStr"/>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B416" t="inlineStr"/>
@@ -12227,7 +12241,7 @@
       <c r="K416" t="inlineStr"/>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B417" t="inlineStr"/>
@@ -12258,7 +12272,7 @@
       <c r="K417" t="inlineStr"/>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B418" t="n">
@@ -12291,7 +12305,7 @@
       <c r="K418" t="inlineStr"/>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B419" t="inlineStr"/>
@@ -12322,7 +12336,7 @@
       <c r="K419" t="inlineStr"/>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B420" t="inlineStr"/>
@@ -12353,7 +12367,7 @@
       <c r="K420" t="inlineStr"/>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B421" t="n">
@@ -12386,7 +12400,7 @@
       <c r="K421" t="inlineStr"/>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B422" t="inlineStr"/>
@@ -12417,7 +12431,7 @@
       <c r="K422" t="inlineStr"/>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B423" t="inlineStr"/>
@@ -12448,7 +12462,7 @@
       <c r="K423" t="inlineStr"/>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B424" t="n">
@@ -12481,7 +12495,7 @@
       <c r="K424" t="inlineStr"/>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B425" t="inlineStr"/>
@@ -12512,7 +12526,7 @@
       <c r="K425" t="inlineStr"/>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -12543,7 +12557,7 @@
       <c r="K426" t="inlineStr"/>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B427" t="n">
@@ -12576,7 +12590,7 @@
       <c r="K427" t="inlineStr"/>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B428" t="inlineStr"/>
@@ -12607,7 +12621,7 @@
       <c r="K428" t="inlineStr"/>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B429" t="inlineStr"/>
@@ -12638,7 +12652,7 @@
       <c r="K429" t="inlineStr"/>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B430" t="n">
@@ -12671,7 +12685,7 @@
       <c r="K430" t="inlineStr"/>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B431" t="inlineStr"/>
@@ -12702,7 +12716,7 @@
       <c r="K431" t="inlineStr"/>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B432" t="inlineStr"/>
@@ -12733,7 +12747,7 @@
       <c r="K432" t="inlineStr"/>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B433" t="n">
@@ -12766,7 +12780,7 @@
       <c r="K433" t="inlineStr"/>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B434" t="inlineStr"/>
@@ -12797,7 +12811,7 @@
       <c r="K434" t="inlineStr"/>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B435" t="inlineStr"/>
@@ -12828,7 +12842,7 @@
       <c r="K435" t="inlineStr"/>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B436" t="n">
@@ -12861,7 +12875,7 @@
       <c r="K436" t="inlineStr"/>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B437" t="inlineStr"/>
@@ -12892,7 +12906,7 @@
       <c r="K437" t="inlineStr"/>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B438" t="inlineStr"/>
@@ -12923,7 +12937,7 @@
       <c r="K438" t="inlineStr"/>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B439" t="n">
@@ -12956,7 +12970,7 @@
       <c r="K439" t="inlineStr"/>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B440" t="inlineStr"/>
@@ -12987,7 +13001,7 @@
       <c r="K440" t="inlineStr"/>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B441" t="inlineStr"/>
@@ -13018,7 +13032,7 @@
       <c r="K441" t="inlineStr"/>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B442" t="n">
@@ -13051,7 +13065,7 @@
       <c r="K442" t="inlineStr"/>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B443" t="inlineStr"/>
@@ -13082,7 +13096,7 @@
       <c r="K443" t="inlineStr"/>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B444" t="inlineStr"/>
@@ -13113,7 +13127,7 @@
       <c r="K444" t="inlineStr"/>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B445" t="n">
@@ -13146,7 +13160,7 @@
       <c r="K445" t="inlineStr"/>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B446" t="inlineStr"/>
@@ -13177,7 +13191,7 @@
       <c r="K446" t="inlineStr"/>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B447" t="inlineStr"/>
@@ -13208,7 +13222,7 @@
       <c r="K447" t="inlineStr"/>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B448" t="n">
@@ -13241,7 +13255,7 @@
       <c r="K448" t="inlineStr"/>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B449" t="inlineStr"/>
@@ -13272,7 +13286,7 @@
       <c r="K449" t="inlineStr"/>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B450" t="inlineStr"/>
@@ -13303,7 +13317,7 @@
       <c r="K450" t="inlineStr"/>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B451" t="n">
@@ -13336,7 +13350,7 @@
       <c r="K451" t="inlineStr"/>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B452" t="inlineStr"/>
@@ -13367,7 +13381,7 @@
       <c r="K452" t="inlineStr"/>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B453" t="inlineStr"/>
@@ -13398,7 +13412,7 @@
       <c r="K453" t="inlineStr"/>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B454" t="n">
@@ -13431,7 +13445,7 @@
       <c r="K454" t="inlineStr"/>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B455" t="inlineStr"/>
@@ -13462,7 +13476,7 @@
       <c r="K455" t="inlineStr"/>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B456" t="inlineStr"/>
@@ -13493,7 +13507,7 @@
       <c r="K456" t="inlineStr"/>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B457" t="n">
@@ -13526,7 +13540,7 @@
       <c r="K457" t="inlineStr"/>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B458" t="inlineStr"/>
@@ -13557,7 +13571,7 @@
       <c r="K458" t="inlineStr"/>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B459" t="inlineStr"/>
@@ -13588,7 +13602,7 @@
       <c r="K459" t="inlineStr"/>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B460" t="n">
@@ -13621,7 +13635,7 @@
       <c r="K460" t="inlineStr"/>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B461" t="inlineStr"/>
@@ -13652,7 +13666,7 @@
       <c r="K461" t="inlineStr"/>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B462" t="inlineStr"/>
@@ -13683,7 +13697,7 @@
       <c r="K462" t="inlineStr"/>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B463" t="n">
@@ -13716,7 +13730,7 @@
       <c r="K463" t="inlineStr"/>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B464" t="inlineStr"/>
@@ -13747,7 +13761,7 @@
       <c r="K464" t="inlineStr"/>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B465" t="inlineStr"/>
@@ -13778,7 +13792,7 @@
       <c r="K465" t="inlineStr"/>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B466" t="n">
@@ -13811,7 +13825,7 @@
       <c r="K466" t="inlineStr"/>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B467" t="inlineStr"/>
@@ -13842,7 +13856,7 @@
       <c r="K467" t="inlineStr"/>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B468" t="inlineStr"/>
@@ -13873,7 +13887,7 @@
       <c r="K468" t="inlineStr"/>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B469" t="n">
@@ -13906,7 +13920,7 @@
       <c r="K469" t="inlineStr"/>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B470" t="inlineStr"/>
@@ -13937,7 +13951,7 @@
       <c r="K470" t="inlineStr"/>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B471" t="inlineStr"/>
@@ -13968,7 +13982,7 @@
       <c r="K471" t="inlineStr"/>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B472" t="n">
@@ -14001,7 +14015,7 @@
       <c r="K472" t="inlineStr"/>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B473" t="inlineStr"/>
@@ -14032,7 +14046,7 @@
       <c r="K473" t="inlineStr"/>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B474" t="inlineStr"/>
@@ -14063,7 +14077,7 @@
       <c r="K474" t="inlineStr"/>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B475" t="n">
@@ -14096,7 +14110,7 @@
       <c r="K475" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B476" t="inlineStr"/>
@@ -14127,7 +14141,7 @@
       <c r="K476" t="inlineStr"/>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B477" t="inlineStr"/>
@@ -14158,7 +14172,7 @@
       <c r="K477" t="inlineStr"/>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B478" t="n">
@@ -14191,7 +14205,7 @@
       <c r="K478" t="inlineStr"/>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B479" t="inlineStr"/>
@@ -14222,7 +14236,7 @@
       <c r="K479" t="inlineStr"/>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B480" t="inlineStr"/>
@@ -14253,7 +14267,7 @@
       <c r="K480" t="inlineStr"/>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B481" t="n">
@@ -14286,7 +14300,7 @@
       <c r="K481" t="inlineStr"/>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B482" t="inlineStr"/>
@@ -14317,7 +14331,7 @@
       <c r="K482" t="inlineStr"/>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B483" t="inlineStr"/>
@@ -14348,7 +14362,7 @@
       <c r="K483" t="inlineStr"/>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B484" t="n">
@@ -14381,7 +14395,7 @@
       <c r="K484" t="inlineStr"/>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B485" t="inlineStr"/>
@@ -14412,7 +14426,7 @@
       <c r="K485" t="inlineStr"/>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B486" t="inlineStr"/>
@@ -14443,7 +14457,7 @@
       <c r="K486" t="inlineStr"/>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B487" t="n">
@@ -14476,7 +14490,7 @@
       <c r="K487" t="inlineStr"/>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B488" t="inlineStr"/>
@@ -14507,7 +14521,7 @@
       <c r="K488" t="inlineStr"/>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B489" t="inlineStr"/>
@@ -14538,7 +14552,7 @@
       <c r="K489" t="inlineStr"/>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B490" t="n">
@@ -14571,7 +14585,7 @@
       <c r="K490" t="inlineStr"/>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B491" t="inlineStr"/>
@@ -14602,7 +14616,7 @@
       <c r="K491" t="inlineStr"/>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B492" t="inlineStr"/>
@@ -14633,7 +14647,7 @@
       <c r="K492" t="inlineStr"/>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B493" t="n">
@@ -14666,7 +14680,7 @@
       <c r="K493" t="inlineStr"/>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B494" t="inlineStr"/>
@@ -14697,7 +14711,7 @@
       <c r="K494" t="inlineStr"/>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B495" t="inlineStr"/>
@@ -14728,7 +14742,7 @@
       <c r="K495" t="inlineStr"/>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B496" t="n">
@@ -14761,7 +14775,7 @@
       <c r="K496" t="inlineStr"/>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B497" t="inlineStr"/>
@@ -14792,7 +14806,7 @@
       <c r="K497" t="inlineStr"/>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B498" t="inlineStr"/>
@@ -14823,7 +14837,7 @@
       <c r="K498" t="inlineStr"/>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B499" t="n">
@@ -14856,7 +14870,7 @@
       <c r="K499" t="inlineStr"/>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B500" t="inlineStr"/>
@@ -14887,7 +14901,7 @@
       <c r="K500" t="inlineStr"/>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B501" t="inlineStr"/>
@@ -14918,7 +14932,7 @@
       <c r="K501" t="inlineStr"/>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B502" t="inlineStr"/>

--- a/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
+++ b/data/nowcast/FR_data_inspect_noreal_sent_levels_auth.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K502"/>
+  <dimension ref="A1:K503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -635,7 +635,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>4.403054001865957</v>
+        <v>4.401829261970061</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -675,7 +675,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>4.513054897080286</v>
+        <v>4.514150787600923</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
@@ -852,7 +852,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>4.553876891600541</v>
+        <v>4.552823705615882</v>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
@@ -911,7 +911,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>4.584967478670572</v>
+        <v>4.585987366571318</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
@@ -1166,7 +1166,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>4.677490847567717</v>
+        <v>4.678420647727684</v>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>4.688591794127164</v>
+        <v>4.689511334421843</v>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
@@ -1891,7 +1891,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>4.561218298458908</v>
+        <v>4.562262684976814</v>
       </c>
       <c r="E71" t="n">
         <v>4.520701029361642</v>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>4.294560608892605</v>
+        <v>4.293195420967266</v>
       </c>
       <c r="E103" t="n">
         <v>4.457829598089382</v>
@@ -3330,7 +3330,7 @@
         <v>6.5</v>
       </c>
       <c r="D130" t="n">
-        <v>4.565389315976247</v>
+        <v>4.564348191467836</v>
       </c>
       <c r="E130" t="n">
         <v>4.546481189639412</v>
@@ -3355,7 +3355,7 @@
         <v>6.75</v>
       </c>
       <c r="D131" t="n">
-        <v>4.526126978647638</v>
+        <v>4.52720864451838</v>
       </c>
       <c r="E131" t="n">
         <v>4.52720864451838</v>
@@ -4866,7 +4866,7 @@
         <v>36616</v>
       </c>
       <c r="B184" t="n">
-        <v>13.08209935219024</v>
+        <v>13.08210018505839</v>
       </c>
       <c r="C184" t="n">
         <v>3.7470435</v>
@@ -4961,7 +4961,7 @@
         <v>36707</v>
       </c>
       <c r="B187" t="n">
-        <v>13.09346974788635</v>
+        <v>13.09348806952728</v>
       </c>
       <c r="C187" t="n">
         <v>4.5017273</v>
@@ -5056,7 +5056,7 @@
         <v>36799</v>
       </c>
       <c r="B190" t="n">
-        <v>13.10136341358678</v>
+        <v>13.10134074220106</v>
       </c>
       <c r="C190" t="n">
         <v>4.8528095</v>
@@ -5151,7 +5151,7 @@
         <v>36891</v>
       </c>
       <c r="B193" t="n">
-        <v>13.107310854478</v>
+        <v>13.10731004234456</v>
       </c>
       <c r="C193" t="n">
         <v>4.9391579</v>
@@ -5246,7 +5246,7 @@
         <v>36981</v>
       </c>
       <c r="B196" t="n">
-        <v>13.11221889570511</v>
+        <v>13.11221990590071</v>
       </c>
       <c r="C196" t="n">
         <v>4.7086364</v>
@@ -5341,7 +5341,7 @@
         <v>37072</v>
       </c>
       <c r="B199" t="n">
-        <v>13.11258916504139</v>
+        <v>13.11260936128016</v>
       </c>
       <c r="C199" t="n">
         <v>4.4535714</v>
@@ -5436,7 +5436,7 @@
         <v>37164</v>
       </c>
       <c r="B202" t="n">
-        <v>13.11843948901369</v>
+        <v>13.11842081571165</v>
       </c>
       <c r="C202" t="n">
         <v>3.98285</v>
@@ -5531,7 +5531,7 @@
         <v>37256</v>
       </c>
       <c r="B205" t="n">
-        <v>13.1139801360248</v>
+        <v>13.11397811918581</v>
       </c>
       <c r="C205" t="n">
         <v>3.3448889</v>
@@ -5626,7 +5626,7 @@
         <v>37346</v>
       </c>
       <c r="B208" t="n">
-        <v>13.11974374917251</v>
+        <v>13.11974274654895</v>
       </c>
       <c r="C208" t="n">
         <v>3.3908</v>
@@ -5721,7 +5721,7 @@
         <v>37437</v>
       </c>
       <c r="B211" t="n">
-        <v>13.12441127902163</v>
+        <v>13.12442844368645</v>
       </c>
       <c r="C211" t="n">
         <v>3.464</v>
@@ -5816,7 +5816,7 @@
         <v>37529</v>
       </c>
       <c r="B214" t="n">
-        <v>13.12852257057188</v>
+        <v>13.12850686746476</v>
       </c>
       <c r="C214" t="n">
         <v>3.3101429</v>
@@ -5911,7 +5911,7 @@
         <v>37621</v>
       </c>
       <c r="B217" t="n">
-        <v>13.12934614106554</v>
+        <v>13.12934018279844</v>
       </c>
       <c r="C217" t="n">
         <v>2.94105</v>
@@ -6006,7 +6006,7 @@
         <v>37711</v>
       </c>
       <c r="B220" t="n">
-        <v>13.13213864342959</v>
+        <v>13.13213507844275</v>
       </c>
       <c r="C220" t="n">
         <v>2.5299524</v>
@@ -6101,7 +6101,7 @@
         <v>37802</v>
       </c>
       <c r="B223" t="n">
-        <v>13.1277848546024</v>
+        <v>13.12779698856574</v>
       </c>
       <c r="C223" t="n">
         <v>2.1518571</v>
@@ -6196,7 +6196,7 @@
         <v>37894</v>
       </c>
       <c r="B226" t="n">
-        <v>13.13884284204811</v>
+        <v>13.1388221850676</v>
       </c>
       <c r="C226" t="n">
         <v>2.1473182</v>
@@ -6291,7 +6291,7 @@
         <v>37986</v>
       </c>
       <c r="B229" t="n">
-        <v>13.14256670872165</v>
+        <v>13.1425727846994</v>
       </c>
       <c r="C229" t="n">
         <v>2.1463333</v>
@@ -6386,7 +6386,7 @@
         <v>38077</v>
       </c>
       <c r="B232" t="n">
-        <v>13.15285068049435</v>
+        <v>13.15285262043797</v>
       </c>
       <c r="C232" t="n">
         <v>2.0288261</v>
@@ -6481,7 +6481,7 @@
         <v>38168</v>
       </c>
       <c r="B235" t="n">
-        <v>13.15731981915444</v>
+        <v>13.15733237249286</v>
       </c>
       <c r="C235" t="n">
         <v>2.1126818</v>
@@ -6576,7 +6576,7 @@
         <v>38260</v>
       </c>
       <c r="B238" t="n">
-        <v>13.16089481459997</v>
+        <v>13.16088653963322</v>
       </c>
       <c r="C238" t="n">
         <v>2.1185909</v>
@@ -6671,7 +6671,7 @@
         <v>38352</v>
       </c>
       <c r="B241" t="n">
-        <v>13.16976457740948</v>
+        <v>13.16976743851948</v>
       </c>
       <c r="C241" t="n">
         <v>2.1731739</v>
@@ -6766,7 +6766,7 @@
         <v>38442</v>
       </c>
       <c r="B244" t="n">
-        <v>13.1726862711054</v>
+        <v>13.17268265759402</v>
       </c>
       <c r="C244" t="n">
         <v>2.1371905</v>
@@ -6861,7 +6861,7 @@
         <v>38533</v>
       </c>
       <c r="B247" t="n">
-        <v>13.17477478646862</v>
+        <v>13.17478598387887</v>
       </c>
       <c r="C247" t="n">
         <v>2.1110455</v>
@@ -6956,7 +6956,7 @@
         <v>38625</v>
       </c>
       <c r="B250" t="n">
-        <v>13.18260995129906</v>
+        <v>13.18260411378147</v>
       </c>
       <c r="C250" t="n">
         <v>2.1391364</v>
@@ -7002,7 +7002,7 @@
         <v>4.738826570800765</v>
       </c>
       <c r="G251" t="n">
-        <v>4.185098925490565</v>
+        <v>4.186619838331271</v>
       </c>
       <c r="H251" t="n">
         <v>9.1</v>
@@ -7051,7 +7051,7 @@
         <v>38717</v>
       </c>
       <c r="B253" t="n">
-        <v>13.18945307901184</v>
+        <v>13.18945401412272</v>
       </c>
       <c r="C253" t="n">
         <v>2.4728571</v>
@@ -7128,7 +7128,7 @@
         <v>4.73795129722191</v>
       </c>
       <c r="G255" t="n">
-        <v>4.2017030805426</v>
+        <v>4.203198967134183</v>
       </c>
       <c r="H255" t="n">
         <v>9.199999999999999</v>
@@ -7146,7 +7146,7 @@
         <v>38807</v>
       </c>
       <c r="B256" t="n">
-        <v>13.19802765217635</v>
+        <v>13.19804823419314</v>
       </c>
       <c r="C256" t="n">
         <v>2.7226087</v>
@@ -7241,7 +7241,7 @@
         <v>38898</v>
       </c>
       <c r="B259" t="n">
-        <v>13.21014767228262</v>
+        <v>13.21014290928743</v>
       </c>
       <c r="C259" t="n">
         <v>2.9856818</v>
@@ -7336,7 +7336,7 @@
         <v>38990</v>
       </c>
       <c r="B262" t="n">
-        <v>13.21092099168603</v>
+        <v>13.21090598146719</v>
       </c>
       <c r="C262" t="n">
         <v>3.335381</v>
@@ -7431,7 +7431,7 @@
         <v>39082</v>
       </c>
       <c r="B265" t="n">
-        <v>13.21618026097844</v>
+        <v>13.21616915343328</v>
       </c>
       <c r="C265" t="n">
         <v>3.6842105</v>
@@ -7526,7 +7526,7 @@
         <v>39172</v>
       </c>
       <c r="B268" t="n">
-        <v>13.22661347677812</v>
+        <v>13.22660716975873</v>
       </c>
       <c r="C268" t="n">
         <v>3.8909091</v>
@@ -7621,7 +7621,7 @@
         <v>39263</v>
       </c>
       <c r="B271" t="n">
-        <v>13.23313236089665</v>
+        <v>13.2331318238092</v>
       </c>
       <c r="C271" t="n">
         <v>4.1477619</v>
@@ -7716,7 +7716,7 @@
         <v>39355</v>
       </c>
       <c r="B274" t="n">
-        <v>13.2365169010101</v>
+        <v>13.23651797155471</v>
       </c>
       <c r="C274" t="n">
         <v>4.7417</v>
@@ -7811,7 +7811,7 @@
         <v>39447</v>
       </c>
       <c r="B277" t="n">
-        <v>13.23701065726901</v>
+        <v>13.23701672067872</v>
       </c>
       <c r="C277" t="n">
         <v>4.8483684</v>
@@ -7906,7 +7906,7 @@
         <v>39538</v>
       </c>
       <c r="B280" t="n">
-        <v>13.2459056191722</v>
+        <v>13.24590844727798</v>
       </c>
       <c r="C280" t="n">
         <v>4.5963684</v>
@@ -8001,7 +8001,7 @@
         <v>39629</v>
       </c>
       <c r="B283" t="n">
-        <v>13.23833748905488</v>
+        <v>13.23834461301571</v>
       </c>
       <c r="C283" t="n">
         <v>4.9405238</v>
@@ -8096,7 +8096,7 @@
         <v>39721</v>
       </c>
       <c r="B286" t="n">
-        <v>13.23615338485734</v>
+        <v>13.23614749470072</v>
       </c>
       <c r="C286" t="n">
         <v>5.0191818</v>
@@ -8191,7 +8191,7 @@
         <v>39813</v>
       </c>
       <c r="B289" t="n">
-        <v>13.22319483233274</v>
+        <v>13.22319428988135</v>
       </c>
       <c r="C289" t="n">
         <v>3.292619</v>
@@ -8286,7 +8286,7 @@
         <v>39903</v>
       </c>
       <c r="B292" t="n">
-        <v>13.20398391656989</v>
+        <v>13.20397949277637</v>
       </c>
       <c r="C292" t="n">
         <v>1.6354545</v>
@@ -8381,7 +8381,7 @@
         <v>39994</v>
       </c>
       <c r="B295" t="n">
-        <v>13.20579179324792</v>
+        <v>13.20578811341339</v>
       </c>
       <c r="C295" t="n">
         <v>1.2279091</v>
@@ -8476,7 +8476,7 @@
         <v>40086</v>
       </c>
       <c r="B298" t="n">
-        <v>13.20809785617297</v>
+        <v>13.20810207821842</v>
       </c>
       <c r="C298" t="n">
         <v>0.7720909</v>
@@ -8513,7 +8513,7 @@
         <v>0.7375</v>
       </c>
       <c r="D299" t="n">
-        <v>4.513054897080286</v>
+        <v>4.514150787600923</v>
       </c>
       <c r="E299" t="n">
         <v>4.590056548178043</v>
@@ -8571,7 +8571,7 @@
         <v>40178</v>
       </c>
       <c r="B301" t="n">
-        <v>13.21530366031098</v>
+        <v>13.21530402481008</v>
       </c>
       <c r="C301" t="n">
         <v>0.7120455</v>
@@ -8666,7 +8666,7 @@
         <v>40268</v>
       </c>
       <c r="B304" t="n">
-        <v>13.21805421202314</v>
+        <v>13.21806784310412</v>
       </c>
       <c r="C304" t="n">
         <v>0.6449565</v>
@@ -8743,7 +8743,7 @@
         <v>4.722953221644475</v>
       </c>
       <c r="G306" t="n">
-        <v>4.302712827954156</v>
+        <v>4.30406509320417</v>
       </c>
       <c r="H306" t="n">
         <v>9.300000000000001</v>
@@ -8761,13 +8761,13 @@
         <v>40359</v>
       </c>
       <c r="B307" t="n">
-        <v>13.22288486382262</v>
+        <v>13.22290457880012</v>
       </c>
       <c r="C307" t="n">
         <v>0.7275909</v>
       </c>
       <c r="D307" t="n">
-        <v>4.565389315976247</v>
+        <v>4.564348191467836</v>
       </c>
       <c r="E307" t="n">
         <v>4.620058798481842</v>
@@ -8856,7 +8856,7 @@
         <v>40451</v>
       </c>
       <c r="B310" t="n">
-        <v>13.22967542757933</v>
+        <v>13.2296786612573</v>
       </c>
       <c r="C310" t="n">
         <v>0.8804999999999999</v>
@@ -8951,7 +8951,7 @@
         <v>40543</v>
       </c>
       <c r="B313" t="n">
-        <v>13.23530377305094</v>
+        <v>13.23527090260729</v>
       </c>
       <c r="C313" t="n">
         <v>1.0216957</v>
@@ -8966,7 +8966,7 @@
         <v>4.592084946439436</v>
       </c>
       <c r="G313" t="n">
-        <v>4.324132656254979</v>
+        <v>4.325456283185487</v>
       </c>
       <c r="H313" t="n">
         <v>9.199999999999999</v>
@@ -9046,7 +9046,7 @@
         <v>40633</v>
       </c>
       <c r="B316" t="n">
-        <v>13.24845896784696</v>
+        <v>13.24837821638581</v>
       </c>
       <c r="C316" t="n">
         <v>1.1755217</v>
@@ -9114,7 +9114,7 @@
         <v>1.4250909</v>
       </c>
       <c r="D318" t="n">
-        <v>4.654912277882906</v>
+        <v>4.653960350157523</v>
       </c>
       <c r="E318" t="n">
         <v>4.672828834461906</v>
@@ -9141,7 +9141,7 @@
         <v>40724</v>
       </c>
       <c r="B319" t="n">
-        <v>13.24853107444841</v>
+        <v>13.24850568787614</v>
       </c>
       <c r="C319" t="n">
         <v>1.4885909</v>
@@ -9178,7 +9178,7 @@
         <v>1.597619</v>
       </c>
       <c r="D320" t="n">
-        <v>4.635699391022914</v>
+        <v>4.634728988229636</v>
       </c>
       <c r="E320" t="n">
         <v>4.654912277882906</v>
@@ -9236,7 +9236,7 @@
         <v>40816</v>
       </c>
       <c r="B322" t="n">
-        <v>13.2518641580147</v>
+        <v>13.25193426256275</v>
       </c>
       <c r="C322" t="n">
         <v>1.5364545</v>
@@ -9273,7 +9273,7 @@
         <v>1.5758571</v>
       </c>
       <c r="D323" t="n">
-        <v>4.534747721691546</v>
+        <v>4.535820107853298</v>
       </c>
       <c r="E323" t="n">
         <v>4.641502115235482</v>
@@ -9331,7 +9331,7 @@
         <v>40908</v>
       </c>
       <c r="B325" t="n">
-        <v>13.25521716550675</v>
+        <v>13.2552499121527</v>
       </c>
       <c r="C325" t="n">
         <v>1.4260952</v>
@@ -9426,13 +9426,13 @@
         <v>40999</v>
       </c>
       <c r="B328" t="n">
-        <v>13.25492957938218</v>
+        <v>13.25486704209737</v>
       </c>
       <c r="C328" t="n">
         <v>0.8584545</v>
       </c>
       <c r="D328" t="n">
-        <v>4.543294782270004</v>
+        <v>4.542230386214217</v>
       </c>
       <c r="E328" t="n">
         <v>4.632785353021065</v>
@@ -9521,7 +9521,7 @@
         <v>41090</v>
       </c>
       <c r="B331" t="n">
-        <v>13.25074726935003</v>
+        <v>13.25070206122244</v>
       </c>
       <c r="C331" t="n">
         <v>0.6588571</v>
@@ -9616,7 +9616,7 @@
         <v>41182</v>
       </c>
       <c r="B334" t="n">
-        <v>13.25403687020132</v>
+        <v>13.25411295854518</v>
       </c>
       <c r="C334" t="n">
         <v>0.2463</v>
@@ -9684,7 +9684,7 @@
         <v>0.192</v>
       </c>
       <c r="D336" t="n">
-        <v>4.437934266612178</v>
+        <v>4.439115601658009</v>
       </c>
       <c r="E336" t="n">
         <v>4.61015772749913</v>
@@ -9711,7 +9711,7 @@
         <v>41274</v>
       </c>
       <c r="B337" t="n">
-        <v>13.25344619972582</v>
+        <v>13.25348567047743</v>
       </c>
       <c r="C337" t="n">
         <v>0.1854737</v>
@@ -9806,7 +9806,7 @@
         <v>41364</v>
       </c>
       <c r="B340" t="n">
-        <v>13.25547315616221</v>
+        <v>13.25541345421498</v>
       </c>
       <c r="C340" t="n">
         <v>0.20605</v>
@@ -9901,7 +9901,7 @@
         <v>41455</v>
       </c>
       <c r="B343" t="n">
-        <v>13.26429617914959</v>
+        <v>13.26425487674955</v>
       </c>
       <c r="C343" t="n">
         <v>0.21025</v>
@@ -9996,7 +9996,7 @@
         <v>41547</v>
       </c>
       <c r="B346" t="n">
-        <v>13.26216984052756</v>
+        <v>13.26224496479565</v>
       </c>
       <c r="C346" t="n">
         <v>0.2232381</v>
@@ -10091,7 +10091,7 @@
         <v>41639</v>
       </c>
       <c r="B349" t="n">
-        <v>13.26823686704048</v>
+        <v>13.26825933773092</v>
       </c>
       <c r="C349" t="n">
         <v>0.2735</v>
@@ -10128,7 +10128,7 @@
         <v>0.2920455</v>
       </c>
       <c r="D350" t="n">
-        <v>4.535820107853298</v>
+        <v>4.536891345234797</v>
       </c>
       <c r="E350" t="n">
         <v>4.61015772749913</v>
@@ -10186,7 +10186,7 @@
         <v>41729</v>
       </c>
       <c r="B352" t="n">
-        <v>13.268159079982</v>
+        <v>13.26811776395057</v>
       </c>
       <c r="C352" t="n">
         <v>0.3053333</v>
@@ -10281,7 +10281,7 @@
         <v>41820</v>
       </c>
       <c r="B355" t="n">
-        <v>13.27044642920849</v>
+        <v>13.27041590121651</v>
       </c>
       <c r="C355" t="n">
         <v>0.2414286</v>
@@ -10318,7 +10318,7 @@
         <v>0.2050435</v>
       </c>
       <c r="D356" t="n">
-        <v>4.507557357121091</v>
+        <v>4.506454213048934</v>
       </c>
       <c r="E356" t="n">
         <v>4.629862798578463</v>
@@ -10376,7 +10376,7 @@
         <v>41912</v>
       </c>
       <c r="B358" t="n">
-        <v>13.27711707537959</v>
+        <v>13.27717669478168</v>
       </c>
       <c r="C358" t="n">
         <v>0.09709089999999999</v>
@@ -10413,7 +10413,7 @@
         <v>0.08260869999999999</v>
       </c>
       <c r="D359" t="n">
-        <v>4.517431271680085</v>
+        <v>4.51852237926242</v>
       </c>
       <c r="E359" t="n">
         <v>4.60816569496789</v>
@@ -10453,7 +10453,7 @@
         <v>4.653960350157523</v>
       </c>
       <c r="G360" t="n">
-        <v>4.394449154672439</v>
+        <v>4.395682961121367</v>
       </c>
       <c r="H360" t="n">
         <v>10.6</v>
@@ -10471,7 +10471,7 @@
         <v>42004</v>
       </c>
       <c r="B361" t="n">
-        <v>13.27418534789149</v>
+        <v>13.2742082007868</v>
       </c>
       <c r="C361" t="n">
         <v>0.0809048</v>
@@ -10566,7 +10566,7 @@
         <v>42094</v>
       </c>
       <c r="B364" t="n">
-        <v>13.27990971402933</v>
+        <v>13.27987947357415</v>
       </c>
       <c r="C364" t="n">
         <v>0.0271818</v>
@@ -10661,13 +10661,13 @@
         <v>42185</v>
       </c>
       <c r="B367" t="n">
-        <v>13.2803287150213</v>
+        <v>13.28026689224328</v>
       </c>
       <c r="C367" t="n">
         <v>-0.0139091</v>
       </c>
       <c r="D367" t="n">
-        <v>4.5685062016165</v>
+        <v>4.56746831880408</v>
       </c>
       <c r="E367" t="n">
         <v>4.632785353021065</v>
@@ -10756,7 +10756,7 @@
         <v>42277</v>
       </c>
       <c r="B370" t="n">
-        <v>13.28332696798937</v>
+        <v>13.28337038452327</v>
       </c>
       <c r="C370" t="n">
         <v>-0.0370455</v>
@@ -10851,7 +10851,7 @@
         <v>42369</v>
       </c>
       <c r="B373" t="n">
-        <v>13.28609453186045</v>
+        <v>13.28612000064311</v>
       </c>
       <c r="C373" t="n">
         <v>-0.1263182</v>
@@ -10946,7 +10946,7 @@
         <v>42460</v>
       </c>
       <c r="B376" t="n">
-        <v>13.28919423715467</v>
+        <v>13.28918391171981</v>
       </c>
       <c r="C376" t="n">
         <v>-0.2285238</v>
@@ -11041,13 +11041,13 @@
         <v>42551</v>
       </c>
       <c r="B379" t="n">
-        <v>13.28662024581101</v>
+        <v>13.28657408503812</v>
       </c>
       <c r="C379" t="n">
         <v>-0.2679091</v>
       </c>
       <c r="D379" t="n">
-        <v>4.575741375297279</v>
+        <v>4.574710978503383</v>
       </c>
       <c r="E379" t="n">
         <v>4.623010104116422</v>
@@ -11109,7 +11109,7 @@
         <v>-0.2982174</v>
       </c>
       <c r="D381" t="n">
-        <v>4.589040804058207</v>
+        <v>4.588024027153121</v>
       </c>
       <c r="E381" t="n">
         <v>4.639571612705423</v>
@@ -11136,7 +11136,7 @@
         <v>42643</v>
       </c>
       <c r="B382" t="n">
-        <v>13.28840072998595</v>
+        <v>13.2884518883589</v>
       </c>
       <c r="C382" t="n">
         <v>-0.3016364</v>
@@ -11231,7 +11231,7 @@
         <v>42735</v>
       </c>
       <c r="B385" t="n">
-        <v>13.29480663741727</v>
+        <v>13.29480613245351</v>
       </c>
       <c r="C385" t="n">
         <v>-0.3157619</v>
@@ -11326,7 +11326,7 @@
         <v>42825</v>
       </c>
       <c r="B388" t="n">
-        <v>13.30140807114214</v>
+        <v>13.30138884138102</v>
       </c>
       <c r="C388" t="n">
         <v>-0.3293478</v>
@@ -11421,7 +11421,7 @@
         <v>42916</v>
       </c>
       <c r="B391" t="n">
-        <v>13.30874966198799</v>
+        <v>13.30871065343922</v>
       </c>
       <c r="C391" t="n">
         <v>-0.33</v>
@@ -11516,7 +11516,7 @@
         <v>43008</v>
       </c>
       <c r="B394" t="n">
-        <v>13.31627369107509</v>
+        <v>13.31630219178847</v>
       </c>
       <c r="C394" t="n">
         <v>-0.329381</v>
@@ -11611,7 +11611,7 @@
         <v>43100</v>
       </c>
       <c r="B397" t="n">
-        <v>13.32225189431731</v>
+        <v>13.32229201579204</v>
       </c>
       <c r="C397" t="n">
         <v>-0.3278947</v>
@@ -11706,7 +11706,7 @@
         <v>43190</v>
       </c>
       <c r="B400" t="n">
-        <v>13.32167314722714</v>
+        <v>13.32164414372599</v>
       </c>
       <c r="C400" t="n">
         <v>-0.3279048</v>
@@ -11801,7 +11801,7 @@
         <v>43281</v>
       </c>
       <c r="B403" t="n">
-        <v>13.3239310341128</v>
+        <v>13.32387724457002</v>
       </c>
       <c r="C403" t="n">
         <v>-0.3220476</v>
@@ -11869,7 +11869,7 @@
         <v>-0.319</v>
       </c>
       <c r="D405" t="n">
-        <v>4.651099117876491</v>
+        <v>4.650143551630823</v>
       </c>
       <c r="E405" t="n">
         <v>4.669083511731744</v>
@@ -11896,7 +11896,7 @@
         <v>43373</v>
       </c>
       <c r="B406" t="n">
-        <v>13.32941933453342</v>
+        <v>13.32947900505622</v>
       </c>
       <c r="C406" t="n">
         <v>-0.31885</v>
@@ -11991,7 +11991,7 @@
         <v>43465</v>
       </c>
       <c r="B409" t="n">
-        <v>13.33659679107678</v>
+        <v>13.33664634947034</v>
       </c>
       <c r="C409" t="n">
         <v>-0.3118947</v>
@@ -12086,7 +12086,7 @@
         <v>43555</v>
       </c>
       <c r="B412" t="n">
-        <v>13.34604870193292</v>
+        <v>13.34593835564056</v>
       </c>
       <c r="C412" t="n">
         <v>-0.3091905</v>
@@ -12181,7 +12181,7 @@
         <v>43646</v>
       </c>
       <c r="B415" t="n">
-        <v>13.35100013340518</v>
+        <v>13.35091388475057</v>
       </c>
       <c r="C415" t="n">
         <v>-0.3289</v>
@@ -12276,7 +12276,7 @@
         <v>43738</v>
       </c>
       <c r="B418" t="n">
-        <v>13.351426175361</v>
+        <v>13.3515653394305</v>
       </c>
       <c r="C418" t="n">
         <v>-0.4175714</v>
@@ -12371,7 +12371,7 @@
         <v>43830</v>
       </c>
       <c r="B421" t="n">
-        <v>13.34638382413335</v>
+        <v>13.34643289987489</v>
       </c>
       <c r="C421" t="n">
         <v>-0.3947</v>
@@ -12420,7 +12420,7 @@
         <v>4.557029810660157</v>
       </c>
       <c r="H422" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I422" t="n">
         <v>4.437697832044343</v>
@@ -12466,7 +12466,7 @@
         <v>43921</v>
       </c>
       <c r="B424" t="n">
-        <v>13.29506077014694</v>
+        <v>13.29486167693759</v>
       </c>
       <c r="C424" t="n">
         <v>-0.4166364</v>
@@ -12543,7 +12543,7 @@
         <v>4.43438186500781</v>
       </c>
       <c r="G426" t="n">
-        <v>4.485259889315534</v>
+        <v>4.484131857611035</v>
       </c>
       <c r="H426" t="n">
         <v>7</v>
@@ -12561,7 +12561,7 @@
         <v>44012</v>
       </c>
       <c r="B427" t="n">
-        <v>13.16481291076443</v>
+        <v>13.16470958572033</v>
       </c>
       <c r="C427" t="n">
         <v>-0.376</v>
@@ -12598,7 +12598,7 @@
         <v>-0.4441304</v>
       </c>
       <c r="D428" t="n">
-        <v>4.423648309364701</v>
+        <v>4.422448549172797</v>
       </c>
       <c r="E428" t="n">
         <v>4.576770711466393</v>
@@ -12610,7 +12610,7 @@
         <v>4.544358046591334</v>
       </c>
       <c r="H428" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I428" t="n">
         <v>4.444884056054749</v>
@@ -12629,7 +12629,7 @@
         <v>-0.4797143</v>
       </c>
       <c r="D429" t="n">
-        <v>4.543294782270004</v>
+        <v>4.542230386214217</v>
       </c>
       <c r="E429" t="n">
         <v>4.585987366571318</v>
@@ -12656,7 +12656,7 @@
         <v>44104</v>
       </c>
       <c r="B430" t="n">
-        <v>13.30583510583056</v>
+        <v>13.30609843473554</v>
       </c>
       <c r="C430" t="n">
         <v>-0.4913636</v>
@@ -12751,7 +12751,7 @@
         <v>44196</v>
       </c>
       <c r="B433" t="n">
-        <v>13.30572672467942</v>
+        <v>13.30576468439151</v>
       </c>
       <c r="C433" t="n">
         <v>-0.5380909</v>
@@ -12819,7 +12819,7 @@
         <v>-0.5411</v>
       </c>
       <c r="D435" t="n">
-        <v>4.549657476057832</v>
+        <v>4.550714000192032</v>
       </c>
       <c r="E435" t="n">
         <v>4.590056548178043</v>
@@ -12846,7 +12846,7 @@
         <v>44286</v>
       </c>
       <c r="B436" t="n">
-        <v>13.31020898184708</v>
+        <v>13.31007504806587</v>
       </c>
       <c r="C436" t="n">
         <v>-0.539087</v>
@@ -12892,7 +12892,7 @@
         <v>4.618086411254637</v>
       </c>
       <c r="G437" t="n">
-        <v>4.531523645819793</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="H437" t="n">
         <v>8.199999999999999</v>
@@ -12941,7 +12941,7 @@
         <v>44377</v>
       </c>
       <c r="B439" t="n">
-        <v>13.322252713139</v>
+        <v>13.32219637664241</v>
       </c>
       <c r="C439" t="n">
         <v>-0.5429091</v>
@@ -13036,7 +13036,7 @@
         <v>44469</v>
       </c>
       <c r="B442" t="n">
-        <v>13.35143730919928</v>
+        <v>13.35158537746141</v>
       </c>
       <c r="C442" t="n">
         <v>-0.5450455</v>
@@ -13051,10 +13051,10 @@
         <v>4.593097604753822</v>
       </c>
       <c r="G442" t="n">
-        <v>4.621043535144381</v>
+        <v>4.622027303054514</v>
       </c>
       <c r="H442" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I442" t="n">
         <v>4.465103197090973</v>
@@ -13073,7 +13073,7 @@
         <v>-0.5498095</v>
       </c>
       <c r="D443" t="n">
-        <v>4.739701078945697</v>
+        <v>4.740574822994295</v>
       </c>
       <c r="E443" t="n">
         <v>4.618086411254637</v>
@@ -13104,7 +13104,7 @@
         <v>-0.5673636</v>
       </c>
       <c r="D444" t="n">
-        <v>4.75960653929251</v>
+        <v>4.760463070394127</v>
       </c>
       <c r="E444" t="n">
         <v>4.597138014290827</v>
@@ -13131,7 +13131,7 @@
         <v>44561</v>
       </c>
       <c r="B445" t="n">
-        <v>13.35654435164127</v>
+        <v>13.35658707653363</v>
       </c>
       <c r="C445" t="n">
         <v>-0.5819565</v>
@@ -13226,7 +13226,7 @@
         <v>44651</v>
       </c>
       <c r="B448" t="n">
-        <v>13.35640477093704</v>
+        <v>13.35630743272554</v>
       </c>
       <c r="C448" t="n">
         <v>-0.4954348</v>
@@ -13321,7 +13321,7 @@
         <v>44742</v>
       </c>
       <c r="B451" t="n">
-        <v>13.36035644685206</v>
+        <v>13.3603001672062</v>
       </c>
       <c r="C451" t="n">
         <v>-0.2392273</v>
@@ -13398,7 +13398,7 @@
         <v>4.5685062016165</v>
       </c>
       <c r="G453" t="n">
-        <v>4.632785353021065</v>
+        <v>4.631812116934513</v>
       </c>
       <c r="H453" t="n">
         <v>7.3</v>
@@ -13416,7 +13416,7 @@
         <v>44834</v>
       </c>
       <c r="B454" t="n">
-        <v>13.36541323691418</v>
+        <v>13.36559249637548</v>
       </c>
       <c r="C454" t="n">
         <v>1.0108636</v>
@@ -13431,7 +13431,7 @@
         <v>4.559126247486684</v>
       </c>
       <c r="G454" t="n">
-        <v>4.652053771886941</v>
+        <v>4.653007515402251</v>
       </c>
       <c r="H454" t="n">
         <v>7.1</v>
@@ -13484,7 +13484,7 @@
         <v>1.8252273</v>
       </c>
       <c r="D456" t="n">
-        <v>4.552823705615882</v>
+        <v>4.553876891600541</v>
       </c>
       <c r="E456" t="n">
         <v>4.616110126026426</v>
@@ -13511,13 +13511,13 @@
         <v>44926</v>
       </c>
       <c r="B457" t="n">
-        <v>13.36944186898186</v>
+        <v>13.369454053746</v>
       </c>
       <c r="C457" t="n">
         <v>2.0634762</v>
       </c>
       <c r="D457" t="n">
-        <v>4.550714000192032</v>
+        <v>4.551769409260976</v>
       </c>
       <c r="E457" t="n">
         <v>4.623991940228679</v>
@@ -13548,7 +13548,7 @@
         <v>2.3448636</v>
       </c>
       <c r="D458" t="n">
-        <v>4.590056548178043</v>
+        <v>4.591071261608589</v>
       </c>
       <c r="E458" t="n">
         <v>4.609162207257629</v>
@@ -13606,7 +13606,7 @@
         <v>45016</v>
       </c>
       <c r="B460" t="n">
-        <v>13.37087895923276</v>
+        <v>13.37075946257252</v>
       </c>
       <c r="C460" t="n">
         <v>2.9105652</v>
@@ -13621,7 +13621,7 @@
         <v>4.593097604753822</v>
       </c>
       <c r="G460" t="n">
-        <v>4.618086411254637</v>
+        <v>4.619073091157083</v>
       </c>
       <c r="H460" t="n">
         <v>7.1</v>
@@ -13652,7 +13652,7 @@
         <v>4.605170185988092</v>
       </c>
       <c r="G461" t="n">
-        <v>4.604169685654508</v>
+        <v>4.603168183317418</v>
       </c>
       <c r="H461" t="n">
         <v>7.3</v>
@@ -13683,7 +13683,7 @@
         <v>4.614129927359564</v>
       </c>
       <c r="G462" t="n">
-        <v>4.614129927359564</v>
+        <v>4.613138355637268</v>
       </c>
       <c r="H462" t="n">
         <v>7.3</v>
@@ -13701,13 +13701,13 @@
         <v>45107</v>
       </c>
       <c r="B463" t="n">
-        <v>13.38014345823182</v>
+        <v>13.38012614814244</v>
       </c>
       <c r="C463" t="n">
         <v>3.5358636</v>
       </c>
       <c r="D463" t="n">
-        <v>4.584967478670572</v>
+        <v>4.583946549536464</v>
       </c>
       <c r="E463" t="n">
         <v>4.621043535144381</v>
@@ -13719,7 +13719,7 @@
         <v>4.620058798481842</v>
       </c>
       <c r="H463" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I463" t="n">
         <v>4.574814065973192</v>
@@ -13738,7 +13738,7 @@
         <v>3.6718095</v>
       </c>
       <c r="D464" t="n">
-        <v>4.559126247486684</v>
+        <v>4.558078578454241</v>
       </c>
       <c r="E464" t="n">
         <v>4.621043535144381</v>
@@ -13747,10 +13747,10 @@
         <v>4.604169685654508</v>
       </c>
       <c r="G464" t="n">
-        <v>4.626931677769604</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="H464" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I464" t="n">
         <v>4.57532934397707</v>
@@ -13778,7 +13778,7 @@
         <v>4.581901559048737</v>
       </c>
       <c r="G465" t="n">
-        <v>4.604169685654508</v>
+        <v>4.603168183317418</v>
       </c>
       <c r="H465" t="n">
         <v>7.5</v>
@@ -13796,7 +13796,7 @@
         <v>45199</v>
       </c>
       <c r="B466" t="n">
-        <v>13.38380860430152</v>
+        <v>13.38406773187141</v>
       </c>
       <c r="C466" t="n">
         <v>3.8800476</v>
@@ -13814,7 +13814,7 @@
         <v>4.614129927359564</v>
       </c>
       <c r="H466" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I466" t="n">
         <v>4.580570069119859</v>
@@ -13833,7 +13833,7 @@
         <v>3.9676364</v>
       </c>
       <c r="D467" t="n">
-        <v>4.544358046591334</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="E467" t="n">
         <v>4.620058798481842</v>
@@ -13873,7 +13873,7 @@
         <v>4.577798989191959</v>
       </c>
       <c r="G468" t="n">
-        <v>4.624972813284271</v>
+        <v>4.625952725170619</v>
       </c>
       <c r="H468" t="n">
         <v>7.6</v>
@@ -13891,7 +13891,7 @@
         <v>45291</v>
       </c>
       <c r="B469" t="n">
-        <v>13.38883795219151</v>
+        <v>13.38879780903058</v>
       </c>
       <c r="C469" t="n">
         <v>3.9348947</v>
@@ -13906,7 +13906,7 @@
         <v>4.584967478670572</v>
       </c>
       <c r="G469" t="n">
-        <v>4.623991940228679</v>
+        <v>4.624972813284271</v>
       </c>
       <c r="H469" t="n">
         <v>7.7</v>
@@ -13986,7 +13986,7 @@
         <v>45382</v>
       </c>
       <c r="B472" t="n">
-        <v>13.39128196146803</v>
+        <v>13.39108661146992</v>
       </c>
       <c r="C472" t="n">
         <v>3.9231</v>
@@ -14081,7 +14081,7 @@
         <v>45473</v>
       </c>
       <c r="B475" t="n">
-        <v>13.39349189261074</v>
+        <v>13.39336622166652</v>
       </c>
       <c r="C475" t="n">
         <v>3.7245</v>
@@ -14127,7 +14127,7 @@
         <v>4.537961436294641</v>
       </c>
       <c r="G476" t="n">
-        <v>4.632785353021065</v>
+        <v>4.631812116934513</v>
       </c>
       <c r="H476" t="n">
         <v>7.5</v>
@@ -14158,7 +14158,7 @@
         <v>4.537961436294641</v>
       </c>
       <c r="G477" t="n">
-        <v>4.65681341913993</v>
+        <v>4.65586330030361</v>
       </c>
       <c r="H477" t="n">
         <v>7.5</v>
@@ -14176,13 +14176,13 @@
         <v>45565</v>
       </c>
       <c r="B478" t="n">
-        <v>13.39783232230842</v>
+        <v>13.39815341912324</v>
       </c>
       <c r="C478" t="n">
         <v>3.4337143</v>
       </c>
       <c r="D478" t="n">
-        <v>4.585987366571318</v>
+        <v>4.584967478670572</v>
       </c>
       <c r="E478" t="n">
         <v>4.623010104116422</v>
@@ -14244,7 +14244,7 @@
         <v>3.0067619</v>
       </c>
       <c r="D480" t="n">
-        <v>4.5685062016165</v>
+        <v>4.56954300834494</v>
       </c>
       <c r="E480" t="n">
         <v>4.621043535144381</v>
@@ -14256,7 +14256,7 @@
         <v>4.647271362006727</v>
       </c>
       <c r="H480" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I480" t="n">
         <v>4.596532992592428</v>
@@ -14271,13 +14271,13 @@
         <v>45657</v>
       </c>
       <c r="B481" t="n">
-        <v>13.39771251084506</v>
+        <v>13.39761577045692</v>
       </c>
       <c r="C481" t="n">
         <v>2.8246</v>
       </c>
       <c r="D481" t="n">
-        <v>4.530446639792155</v>
+        <v>4.531523645819793</v>
       </c>
       <c r="E481" t="n">
         <v>4.618086411254637</v>
@@ -14286,7 +14286,7 @@
         <v>4.55597994179732</v>
       </c>
       <c r="G481" t="n">
-        <v>4.643428898105181</v>
+        <v>4.644390899141372</v>
       </c>
       <c r="H481" t="n">
         <v>7.3</v>
@@ -14317,7 +14317,7 @@
         <v>4.51852237926242</v>
       </c>
       <c r="G482" t="n">
-        <v>4.652053771886941</v>
+        <v>4.653007515402251</v>
       </c>
       <c r="H482" t="n">
         <v>7.3</v>
@@ -14366,7 +14366,7 @@
         <v>45747</v>
       </c>
       <c r="B484" t="n">
-        <v>13.39939538874882</v>
+        <v>13.39928076800916</v>
       </c>
       <c r="C484" t="n">
         <v>2.4424286</v>
@@ -14412,7 +14412,7 @@
         <v>4.520701029361642</v>
       </c>
       <c r="G485" t="n">
-        <v>4.665324108807838</v>
+        <v>4.666265285347902</v>
       </c>
       <c r="H485" t="n">
         <v>7.5</v>
@@ -14461,7 +14461,7 @@
         <v>45838</v>
       </c>
       <c r="B487" t="n">
-        <v>13.40175175202838</v>
+        <v>13.40162998898713</v>
       </c>
       <c r="C487" t="n">
         <v>1.983619</v>
@@ -14510,7 +14510,7 @@
         <v>4.665324108807838</v>
       </c>
       <c r="H488" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I488" t="n">
         <v>4.611351045063173</v>
@@ -14529,7 +14529,7 @@
         <v>2.0210952</v>
       </c>
       <c r="D489" t="n">
-        <v>4.529368472571809</v>
+        <v>4.528289141652134</v>
       </c>
       <c r="E489" t="n">
         <v>4.625952725170619</v>
@@ -14538,7 +14538,7 @@
         <v>4.530446639792155</v>
       </c>
       <c r="G489" t="n">
-        <v>4.671893818030999</v>
+        <v>4.670957926526095</v>
       </c>
       <c r="H489" t="n">
         <v>7.8</v>
@@ -14556,7 +14556,7 @@
         <v>45930</v>
       </c>
       <c r="B490" t="n">
-        <v>13.40598019790527</v>
+        <v>13.40629643105908</v>
       </c>
       <c r="C490" t="n">
         <v>2.0272727</v>
@@ -14571,7 +14571,7 @@
         <v>4.511957804265912</v>
       </c>
       <c r="G490" t="n">
-        <v>4.671893818030999</v>
+        <v>4.672828834461906</v>
       </c>
       <c r="H490" t="n">
         <v>7.9</v>
@@ -14593,7 +14593,7 @@
         <v>2.0344348</v>
       </c>
       <c r="D491" t="n">
-        <v>4.551769409260976</v>
+        <v>4.552823705615882</v>
       </c>
       <c r="E491" t="n">
         <v>4.638604962074329</v>
@@ -14633,10 +14633,10 @@
         <v>4.502029427068578</v>
       </c>
       <c r="G492" t="n">
-        <v>4.680277658474897</v>
+        <v>4.681204872264089</v>
       </c>
       <c r="H492" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I492" t="n">
         <v>4.604369865817322</v>
@@ -14651,13 +14651,13 @@
         <v>46022</v>
       </c>
       <c r="B493" t="n">
-        <v>13.40860611450979</v>
+        <v>13.40858989104417</v>
       </c>
       <c r="C493" t="n">
         <v>2.0484286</v>
       </c>
       <c r="D493" t="n">
-        <v>4.547541073151455</v>
+        <v>4.548599834499697</v>
       </c>
       <c r="E493" t="n">
         <v>4.633757642840004</v>
@@ -14666,7 +14666,7 @@
         <v>4.51852237926242</v>
       </c>
       <c r="G493" t="n">
-        <v>4.681204872264089</v>
+        <v>4.68213122712422</v>
       </c>
       <c r="H493" t="n">
         <v>8</v>
@@ -14700,7 +14700,7 @@
         <v>4.684905154006945</v>
       </c>
       <c r="H494" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I494" t="n">
         <v>4.601061757943548</v>
@@ -14746,13 +14746,13 @@
         <v>46112</v>
       </c>
       <c r="B496" t="n">
-        <v>13.40680565739153</v>
+        <v>13.40689128069045</v>
       </c>
       <c r="C496" t="n">
         <v>2.1094091</v>
       </c>
       <c r="D496" t="n">
-        <v>4.561218298458908</v>
+        <v>4.560172820057356</v>
       </c>
       <c r="E496" t="n">
         <v>4.639571612705423</v>
@@ -14783,7 +14783,7 @@
         <v>2.1753</v>
       </c>
       <c r="D497" t="n">
-        <v>4.531523645819793</v>
+        <v>4.530446639792155</v>
       </c>
       <c r="E497" t="n">
         <v>4.639571612705423</v>
@@ -14814,7 +14814,7 @@
         <v>2.2261</v>
       </c>
       <c r="D498" t="n">
-        <v>4.546481189639412</v>
+        <v>4.545420181582317</v>
       </c>
       <c r="E498" t="n">
         <v>4.638604962074329</v>
@@ -14823,7 +14823,7 @@
         <v>4.504244267398131</v>
       </c>
       <c r="G498" t="n">
-        <v>4.685828089005546</v>
+        <v>4.686750172980514</v>
       </c>
       <c r="H498" t="n">
         <v>8.4</v>
@@ -14841,7 +14841,7 @@
         <v>46203</v>
       </c>
       <c r="B499" t="n">
-        <v>13.40715984048713</v>
+        <v>13.40689639678902</v>
       </c>
       <c r="C499" t="n">
         <v>2.339</v>
@@ -14887,7 +14887,7 @@
         <v>4.472780997942346</v>
       </c>
       <c r="G500" t="n">
-        <v>4.69866052907543</v>
+        <v>4.695010889987881</v>
       </c>
       <c r="H500" t="n">
         <v>8.300000000000001</v>
@@ -14918,10 +14918,10 @@
         <v>4.479606963012746</v>
       </c>
       <c r="G501" t="n">
-        <v>4.687671407499835</v>
+        <v>4.697749367281185</v>
       </c>
       <c r="H501" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I501" t="n">
         <v>4.642080540008188</v>
@@ -14935,17 +14935,23 @@
       <c r="A502" s="2" t="n">
         <v>46295</v>
       </c>
-      <c r="B502" t="inlineStr"/>
+      <c r="B502" t="n">
+        <v>13.40558536846352</v>
+      </c>
       <c r="C502" t="n">
         <v>2.6350455</v>
       </c>
       <c r="D502" t="n">
-        <v>4.566429357671661</v>
+        <v>4.564348191467836</v>
       </c>
       <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr"/>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
+      <c r="G502" t="n">
+        <v>4.691347882229143</v>
+      </c>
+      <c r="H502" t="n">
+        <v>8.5</v>
+      </c>
       <c r="I502" t="n">
         <v>4.639088404191552</v>
       </c>
@@ -14953,6 +14959,23 @@
         <v>4.596689494135473</v>
       </c>
       <c r="K502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="2" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="n">
+        <v>4.565389315976247</v>
+      </c>
+      <c r="E503" t="inlineStr"/>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
